--- a/docs/BlueFox_CUO_Audit_Consolidation.xlsx
+++ b/docs/BlueFox_CUO_Audit_Consolidation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\Minijeu Yllias\V3_BlueFox odyssey Fondation IA\V3_EXECUTABL_fondation IA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5A3422-60CC-43E9-B9DA-6C70DC50883D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F73673F-6D5F-441A-9550-9AFCC684C398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="1755" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="688">
   <si>
     <t>BlueFox Odyssey — CUO documentaire consolidé</t>
   </si>
@@ -755,9 +755,6 @@
     <t>stable · repéré · observé · analysé · contaminé · régénéré</t>
   </si>
   <si>
-    <t>biology · chemistry · energy</t>
-  </si>
-  <si>
     <t>Observation d’un phénomène · prélèvement indirect · étude environnementale</t>
   </si>
   <si>
@@ -1007,9 +1004,6 @@
     <t>non-extractable</t>
   </si>
   <si>
-    <t>botany · bioluminescence · adaptation</t>
-  </si>
-  <si>
     <t>Étude de la flore · repère nocturne · analyse écologique</t>
   </si>
   <si>
@@ -1170,12 +1164,6 @@
   </si>
   <si>
     <t>stable · résonnant · observé · analysé · fracturé</t>
-  </si>
-  <si>
-    <t>botany · crystallography · energy</t>
-  </si>
-  <si>
-    <t>Identifier une espèce · signature énergétique · cartographie de biome</t>
   </si>
   <si>
     <t>decor · plant · mineral · glowing · landmark</t>
@@ -2083,6 +2071,36 @@
   </si>
   <si>
     <t>selon standing avec l'espèce</t>
+  </si>
+  <si>
+    <t>biology + botany</t>
+  </si>
+  <si>
+    <t>revoir l'esthetique du modèle plutôt en forme de haricot qu'un dique parfait, cela offrera différentes possibilités de placement/rotation</t>
+  </si>
+  <si>
+    <t>biology · chemistry · energy - enineering</t>
+  </si>
+  <si>
+    <t>botany · bioluminescence · adaptation· energy - enineering</t>
+  </si>
+  <si>
+    <t>forest · crystalline · alien + magentic</t>
+  </si>
+  <si>
+    <t>forest · jungle · swamp · alien - Magnetic</t>
+  </si>
+  <si>
+    <t>Clairière luminescente · forêt photoréactive  magnetic</t>
+  </si>
+  <si>
+    <t>Forêt cristalline · bosquet résonnant - magnetic plaine</t>
+  </si>
+  <si>
+    <t>botany · crystallography · energy - engineering</t>
+  </si>
+  <si>
+    <t>Identifier une espèce · signature énergétique · cartographie de biome - compréhension du monde mineral</t>
   </si>
 </sst>
 </file>
@@ -3527,7 +3545,7 @@
   <autoFilter ref="A1:BC40" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="52">
       <filters>
-        <filter val="P1"/>
+        <filter val="P2"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3974,7 +3992,7 @@
       </c>
       <c r="B11" s="10">
         <f>COUNTIF(CUO_Master!$BB$2:$BB$40,"Validé")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -4246,7 +4264,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:55" ht="62.1" customHeight="1">
+    <row r="2" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>77</v>
       </c>
@@ -4407,11 +4425,11 @@
         <v>8</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="BC2" s="31"/>
     </row>
-    <row r="3" spans="1:55" ht="62.1" customHeight="1">
+    <row r="3" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>110</v>
       </c>
@@ -4572,11 +4590,11 @@
         <v>8</v>
       </c>
       <c r="BB3" s="33" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="BC3" s="34"/>
     </row>
-    <row r="4" spans="1:55" ht="62.1" customHeight="1">
+    <row r="4" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A4" s="32" t="s">
         <v>128</v>
       </c>
@@ -4737,11 +4755,11 @@
         <v>8</v>
       </c>
       <c r="BB4" s="33" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="BC4" s="34"/>
     </row>
-    <row r="5" spans="1:55" ht="62.1" customHeight="1">
+    <row r="5" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A5" s="32" t="s">
         <v>145</v>
       </c>
@@ -4842,13 +4860,13 @@
         <v>122</v>
       </c>
       <c r="AH5" s="35" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="AI5" s="33" t="s">
         <v>158</v>
       </c>
       <c r="AJ5" s="35" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="AK5" s="33" t="s">
         <v>103</v>
@@ -4906,7 +4924,7 @@
       </c>
       <c r="BC5" s="34"/>
     </row>
-    <row r="6" spans="1:55" ht="62.1" customHeight="1">
+    <row r="6" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A6" s="32" t="s">
         <v>160</v>
       </c>
@@ -5067,10 +5085,10 @@
         <v>8</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC6" s="36" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" spans="1:55" ht="62.1" hidden="1" customHeight="1">
@@ -5238,7 +5256,7 @@
       </c>
       <c r="BC7" s="34"/>
     </row>
-    <row r="8" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="8" spans="1:55" ht="62.1" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>191</v>
       </c>
@@ -5318,7 +5336,7 @@
         <v>89</v>
       </c>
       <c r="AA8" s="33" t="s">
-        <v>96</v>
+        <v>672</v>
       </c>
       <c r="AB8" s="33" t="s">
         <v>97</v>
@@ -5339,7 +5357,7 @@
         <v>122</v>
       </c>
       <c r="AH8" s="33" t="s">
-        <v>91</v>
+        <v>678</v>
       </c>
       <c r="AI8" s="33" t="s">
         <v>158</v>
@@ -5399,11 +5417,11 @@
         <v>203</v>
       </c>
       <c r="BB8" s="33" t="s">
-        <v>109</v>
+        <v>638</v>
       </c>
       <c r="BC8" s="34"/>
     </row>
-    <row r="9" spans="1:55" ht="62.1" customHeight="1">
+    <row r="9" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A9" s="32" t="s">
         <v>204</v>
       </c>
@@ -5564,13 +5582,13 @@
         <v>8</v>
       </c>
       <c r="BB9" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC9" s="34" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="10" spans="1:55" ht="62.1" customHeight="1">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>218</v>
       </c>
@@ -5632,7 +5650,7 @@
         <v>91</v>
       </c>
       <c r="U10" s="35" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="V10" s="33" t="s">
         <v>97</v>
@@ -5731,13 +5749,13 @@
         <v>8</v>
       </c>
       <c r="BB10" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="BC10" s="36" t="s">
         <v>652</v>
       </c>
-      <c r="BC10" s="36" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="11" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    </row>
+    <row r="11" spans="1:55" ht="62.1" customHeight="1">
       <c r="A11" s="32" t="s">
         <v>229</v>
       </c>
@@ -5808,7 +5826,7 @@
         <v>97</v>
       </c>
       <c r="X11" s="33" t="s">
-        <v>97</v>
+        <v>654</v>
       </c>
       <c r="Y11" s="33" t="s">
         <v>97</v>
@@ -5838,19 +5856,19 @@
         <v>233</v>
       </c>
       <c r="AH11" s="33" t="s">
-        <v>239</v>
+        <v>680</v>
       </c>
       <c r="AI11" s="33" t="s">
         <v>142</v>
       </c>
       <c r="AJ11" s="33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AK11" s="33" t="s">
         <v>187</v>
       </c>
       <c r="AL11" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AM11" s="33">
         <v>8</v>
@@ -5898,19 +5916,21 @@
         <v>203</v>
       </c>
       <c r="BB11" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="BC11" s="34"/>
+        <v>648</v>
+      </c>
+      <c r="BC11" s="34" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="12" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A12" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="C12" s="33" t="s">
         <v>243</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>244</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>80</v>
@@ -5919,7 +5939,7 @@
         <v>178</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="33" t="s">
         <v>178</v>
@@ -5934,10 +5954,10 @@
         <v>85</v>
       </c>
       <c r="K12" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="L12" s="33" t="s">
         <v>246</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>247</v>
       </c>
       <c r="M12" s="33" t="s">
         <v>88</v>
@@ -5946,25 +5966,25 @@
         <v>89</v>
       </c>
       <c r="O12" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="P12" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="P12" s="33" t="s">
+      <c r="Q12" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="Q12" s="33" t="s">
+      <c r="R12" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="R12" s="33" t="s">
+      <c r="S12" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T12" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="33" t="s">
         <v>251</v>
-      </c>
-      <c r="S12" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T12" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U12" s="33" t="s">
-        <v>252</v>
       </c>
       <c r="V12" s="33" t="s">
         <v>97</v>
@@ -6006,16 +6026,16 @@
         <v>91</v>
       </c>
       <c r="AI12" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ12" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="AJ12" s="33" t="s">
+      <c r="AK12" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL12" s="33" t="s">
         <v>254</v>
-      </c>
-      <c r="AK12" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL12" s="33" t="s">
-        <v>255</v>
       </c>
       <c r="AM12" s="33">
         <v>1</v>
@@ -6069,13 +6089,13 @@
     </row>
     <row r="13" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A13" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="33" t="s">
         <v>257</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>258</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>80</v>
@@ -6084,7 +6104,7 @@
         <v>178</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>178</v>
@@ -6096,16 +6116,16 @@
         <v>84</v>
       </c>
       <c r="J13" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="K13" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="K13" s="33" t="s">
+      <c r="L13" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="L13" s="33" t="s">
+      <c r="M13" s="33" t="s">
         <v>262</v>
-      </c>
-      <c r="M13" s="33" t="s">
-        <v>263</v>
       </c>
       <c r="N13" s="33" t="s">
         <v>89</v>
@@ -6114,14 +6134,14 @@
         <v>118</v>
       </c>
       <c r="P13" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q13" s="33" t="s">
         <v>264</v>
       </c>
-      <c r="Q13" s="33" t="s">
+      <c r="R13" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="R13" s="33" t="s">
-        <v>266</v>
-      </c>
       <c r="S13" s="33" t="s">
         <v>91</v>
       </c>
@@ -6129,7 +6149,7 @@
         <v>91</v>
       </c>
       <c r="U13" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V13" s="33" t="s">
         <v>97</v>
@@ -6174,13 +6194,13 @@
         <v>158</v>
       </c>
       <c r="AJ13" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK13" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL13" s="33" t="s">
         <v>267</v>
-      </c>
-      <c r="AK13" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL13" s="33" t="s">
-        <v>268</v>
       </c>
       <c r="AM13" s="33">
         <v>1</v>
@@ -6232,15 +6252,15 @@
       </c>
       <c r="BC13" s="34"/>
     </row>
-    <row r="14" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="14" spans="1:55" ht="62.1" customHeight="1">
       <c r="A14" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="C14" s="33" t="s">
         <v>270</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>271</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>80</v>
@@ -6249,7 +6269,7 @@
         <v>178</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G14" s="33" t="s">
         <v>178</v>
@@ -6261,16 +6281,16 @@
         <v>132</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="K14" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="L14" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="L14" s="33" t="s">
+      <c r="M14" s="33" t="s">
         <v>275</v>
-      </c>
-      <c r="M14" s="33" t="s">
-        <v>276</v>
       </c>
       <c r="N14" s="33" t="s">
         <v>89</v>
@@ -6282,11 +6302,11 @@
         <v>151</v>
       </c>
       <c r="Q14" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="R14" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="R14" s="33" t="s">
-        <v>278</v>
-      </c>
       <c r="S14" s="33" t="s">
         <v>91</v>
       </c>
@@ -6294,7 +6314,7 @@
         <v>91</v>
       </c>
       <c r="U14" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V14" s="33" t="s">
         <v>97</v>
@@ -6339,13 +6359,13 @@
         <v>158</v>
       </c>
       <c r="AJ14" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="AK14" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL14" s="33" t="s">
         <v>279</v>
-      </c>
-      <c r="AK14" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL14" s="33" t="s">
-        <v>280</v>
       </c>
       <c r="AM14" s="33">
         <v>1</v>
@@ -6393,19 +6413,19 @@
         <v>203</v>
       </c>
       <c r="BB14" s="33" t="s">
-        <v>109</v>
+        <v>638</v>
       </c>
       <c r="BC14" s="34"/>
     </row>
-    <row r="15" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="15" spans="1:55" ht="62.1" customHeight="1">
       <c r="A15" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="33" t="s">
         <v>282</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>283</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>80</v>
@@ -6414,7 +6434,7 @@
         <v>207</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G15" s="33" t="s">
         <v>207</v>
@@ -6429,13 +6449,13 @@
         <v>222</v>
       </c>
       <c r="K15" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="L15" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="L15" s="33" t="s">
+      <c r="M15" s="33" t="s">
         <v>286</v>
-      </c>
-      <c r="M15" s="33" t="s">
-        <v>287</v>
       </c>
       <c r="N15" s="33" t="s">
         <v>89</v>
@@ -6444,14 +6464,14 @@
         <v>211</v>
       </c>
       <c r="P15" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q15" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="Q15" s="33" t="s">
+      <c r="R15" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="R15" s="33" t="s">
-        <v>290</v>
-      </c>
       <c r="S15" s="33" t="s">
         <v>91</v>
       </c>
@@ -6459,7 +6479,7 @@
         <v>91</v>
       </c>
       <c r="U15" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V15" s="33" t="s">
         <v>97</v>
@@ -6501,16 +6521,16 @@
         <v>91</v>
       </c>
       <c r="AI15" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AJ15" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="AK15" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL15" s="33" t="s">
         <v>291</v>
-      </c>
-      <c r="AK15" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL15" s="33" t="s">
-        <v>292</v>
       </c>
       <c r="AM15" s="33">
         <v>1</v>
@@ -6558,28 +6578,28 @@
         <v>203</v>
       </c>
       <c r="BB15" s="33" t="s">
-        <v>109</v>
+        <v>638</v>
       </c>
       <c r="BC15" s="34"/>
     </row>
-    <row r="16" spans="1:55" ht="62.1" customHeight="1">
+    <row r="16" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A16" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="C16" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="D16" s="33" t="s">
         <v>295</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>296</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G16" s="33" t="s">
         <v>78</v>
@@ -6600,7 +6620,7 @@
         <v>91</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="N16" s="33" t="s">
         <v>97</v>
@@ -6612,10 +6632,10 @@
         <v>91</v>
       </c>
       <c r="Q16" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="R16" s="33" t="s">
         <v>298</v>
-      </c>
-      <c r="R16" s="33" t="s">
-        <v>299</v>
       </c>
       <c r="S16" s="33" t="s">
         <v>91</v>
@@ -6624,28 +6644,28 @@
         <v>156</v>
       </c>
       <c r="U16" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="V16" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="V16" s="33" t="s">
+      <c r="W16" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X16" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y16" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W16" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X16" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y16" s="33" t="s">
+      <c r="Z16" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z16" s="33" t="s">
-        <v>303</v>
-      </c>
       <c r="AA16" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AB16" s="35" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AC16" s="33" t="s">
         <v>91</v>
@@ -6654,7 +6674,7 @@
         <v>90</v>
       </c>
       <c r="AE16" s="33" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AF16" s="33" t="s">
         <v>98</v>
@@ -6663,58 +6683,58 @@
         <v>99</v>
       </c>
       <c r="AH16" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="AI16" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="AI16" s="33" t="s">
+      <c r="AJ16" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="AJ16" s="33" t="s">
+      <c r="AK16" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="AK16" s="33" t="s">
+      <c r="AL16" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="AL16" s="33" t="s">
-        <v>310</v>
-      </c>
       <c r="AM16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR16" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS16" s="33" t="s">
         <v>105</v>
       </c>
       <c r="AT16" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU16" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV16" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW16" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU16" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV16" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW16" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX16" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY16" s="33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AZ16" s="33" t="s">
         <v>108</v>
@@ -6723,30 +6743,30 @@
         <v>8</v>
       </c>
       <c r="BB16" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC16" s="36" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="17" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" ht="62.1" customHeight="1">
       <c r="A17" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>317</v>
-      </c>
       <c r="D17" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>122</v>
@@ -6767,7 +6787,7 @@
         <v>91</v>
       </c>
       <c r="M17" s="33" t="s">
-        <v>319</v>
+        <v>683</v>
       </c>
       <c r="N17" s="33" t="s">
         <v>97</v>
@@ -6779,10 +6799,10 @@
         <v>91</v>
       </c>
       <c r="Q17" s="33" t="s">
+        <v>684</v>
+      </c>
+      <c r="R17" s="33" t="s">
         <v>320</v>
-      </c>
-      <c r="R17" s="33" t="s">
-        <v>321</v>
       </c>
       <c r="S17" s="33" t="s">
         <v>91</v>
@@ -6794,25 +6814,25 @@
         <v>168</v>
       </c>
       <c r="V17" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W17" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X17" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y17" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W17" s="33" t="s">
+      <c r="Z17" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA17" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB17" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X17" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y17" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z17" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA17" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB17" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC17" s="33" t="s">
         <v>91</v>
@@ -6824,64 +6844,64 @@
         <v>91</v>
       </c>
       <c r="AF17" s="33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG17" s="33" t="s">
         <v>122</v>
       </c>
       <c r="AH17" s="33" t="s">
+        <v>681</v>
+      </c>
+      <c r="AI17" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ17" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="AK17" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="AL17" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="AI17" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="AJ17" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="AK17" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="AL17" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="AM17" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AN17" s="33" t="s">
-        <v>311</v>
+      <c r="AM17" s="33">
+        <v>3</v>
+      </c>
+      <c r="AN17" s="33">
+        <v>5</v>
       </c>
       <c r="AO17" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP17" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ17" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR17" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS17" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT17" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU17" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV17" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW17" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU17" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV17" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW17" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX17" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY17" s="33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AZ17" s="33" t="s">
         <v>108</v>
@@ -6890,33 +6910,33 @@
         <v>203</v>
       </c>
       <c r="BB17" s="33" t="s">
-        <v>109</v>
+        <v>648</v>
       </c>
       <c r="BC17" s="34" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="18" spans="1:55" ht="62.1" customHeight="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A18" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="D18" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="F18" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>331</v>
-      </c>
       <c r="G18" s="33" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H18" s="33" t="s">
         <v>114</v>
@@ -6934,7 +6954,7 @@
         <v>91</v>
       </c>
       <c r="M18" s="33" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N18" s="33" t="s">
         <v>97</v>
@@ -6946,40 +6966,40 @@
         <v>91</v>
       </c>
       <c r="Q18" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="R18" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="S18" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T18" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U18" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="R18" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="S18" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U18" s="33" t="s">
-        <v>335</v>
-      </c>
       <c r="V18" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W18" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X18" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y18" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W18" s="33" t="s">
+      <c r="Z18" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA18" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB18" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X18" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y18" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z18" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA18" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB18" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC18" s="33" t="s">
         <v>91</v>
@@ -6988,67 +7008,67 @@
         <v>169</v>
       </c>
       <c r="AE18" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="AF18" s="33" t="s">
         <v>328</v>
-      </c>
-      <c r="AF18" s="33" t="s">
-        <v>330</v>
       </c>
       <c r="AG18" s="33" t="s">
         <v>162</v>
       </c>
       <c r="AH18" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="AI18" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ18" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="AK18" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="AL18" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="AI18" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="AJ18" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="AK18" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="AL18" s="33" t="s">
-        <v>338</v>
-      </c>
       <c r="AM18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR18" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS18" s="33" t="s">
         <v>127</v>
       </c>
       <c r="AT18" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU18" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV18" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW18" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU18" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV18" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW18" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX18" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY18" s="33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AZ18" s="33" t="s">
         <v>108</v>
@@ -7057,30 +7077,30 @@
         <v>8</v>
       </c>
       <c r="BB18" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC18" s="36" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="19" spans="1:55" ht="62.1" customHeight="1">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="19" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A19" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>339</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="D19" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="F19" s="33" t="s">
         <v>341</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>343</v>
       </c>
       <c r="G19" s="33" t="s">
         <v>162</v>
@@ -7101,7 +7121,7 @@
         <v>91</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N19" s="33" t="s">
         <v>97</v>
@@ -7113,40 +7133,40 @@
         <v>91</v>
       </c>
       <c r="Q19" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="R19" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="S19" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T19" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U19" s="33" t="s">
         <v>345</v>
       </c>
-      <c r="R19" s="33" t="s">
-        <v>346</v>
-      </c>
-      <c r="S19" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T19" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U19" s="33" t="s">
-        <v>347</v>
-      </c>
       <c r="V19" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W19" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X19" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y19" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W19" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X19" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y19" s="33" t="s">
+      <c r="Z19" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z19" s="33" t="s">
+      <c r="AA19" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB19" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="AA19" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB19" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC19" s="33" t="s">
         <v>91</v>
@@ -7155,67 +7175,67 @@
         <v>169</v>
       </c>
       <c r="AE19" s="33" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AF19" s="33" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG19" s="33" t="s">
         <v>162</v>
       </c>
       <c r="AH19" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="AI19" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ19" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK19" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="AL19" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="AI19" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="AJ19" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="AK19" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="AL19" s="33" t="s">
-        <v>352</v>
-      </c>
       <c r="AM19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR19" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS19" s="33" t="s">
         <v>105</v>
       </c>
       <c r="AT19" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU19" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV19" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW19" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU19" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV19" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW19" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX19" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY19" s="33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AZ19" s="33" t="s">
         <v>108</v>
@@ -7224,39 +7244,39 @@
         <v>8</v>
       </c>
       <c r="BB19" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC19" s="34" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+      <c r="A20" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="20" spans="1:55" ht="62.1" customHeight="1">
-      <c r="A20" s="32" t="s">
+      <c r="C20" s="33" t="s">
         <v>354</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="D20" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>355</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="F20" s="33" t="s">
         <v>356</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E20" s="33" t="s">
+      <c r="G20" s="33" t="s">
         <v>357</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>359</v>
       </c>
       <c r="H20" s="33" t="s">
         <v>221</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J20" s="33" t="s">
         <v>91</v>
@@ -7268,7 +7288,7 @@
         <v>91</v>
       </c>
       <c r="M20" s="33" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="N20" s="33" t="s">
         <v>97</v>
@@ -7280,40 +7300,40 @@
         <v>91</v>
       </c>
       <c r="Q20" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="R20" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="S20" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T20" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U20" s="33" t="s">
         <v>362</v>
       </c>
-      <c r="R20" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="S20" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T20" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U20" s="33" t="s">
-        <v>364</v>
-      </c>
       <c r="V20" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W20" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X20" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y20" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W20" s="33" t="s">
+      <c r="Z20" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA20" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB20" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X20" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y20" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z20" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA20" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB20" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC20" s="33" t="s">
         <v>91</v>
@@ -7325,64 +7345,64 @@
         <v>91</v>
       </c>
       <c r="AF20" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG20" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="AH20" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="AI20" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ20" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="AG20" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="AH20" s="33" t="s">
+      <c r="AK20" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="AL20" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="AI20" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="AJ20" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="AK20" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="AL20" s="33" t="s">
-        <v>368</v>
-      </c>
       <c r="AM20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS20" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT20" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU20" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV20" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW20" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU20" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV20" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW20" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX20" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY20" s="33" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AZ20" s="33" t="s">
         <v>108</v>
@@ -7391,33 +7411,33 @@
         <v>8</v>
       </c>
       <c r="BB20" s="33" t="s">
+        <v>653</v>
+      </c>
+      <c r="BC20" s="36" t="s">
         <v>657</v>
       </c>
-      <c r="BC20" s="36" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="21" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    </row>
+    <row r="21" spans="1:55" ht="62.1" customHeight="1">
       <c r="A21" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="C21" s="33" t="s">
         <v>371</v>
       </c>
-      <c r="B21" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>373</v>
-      </c>
       <c r="D21" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F21" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="G21" s="33" t="s">
         <v>372</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>374</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>195</v>
@@ -7435,7 +7455,7 @@
         <v>91</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>375</v>
+        <v>682</v>
       </c>
       <c r="N21" s="33" t="s">
         <v>97</v>
@@ -7447,10 +7467,10 @@
         <v>91</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>376</v>
+        <v>685</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S21" s="33" t="s">
         <v>91</v>
@@ -7462,25 +7482,25 @@
         <v>168</v>
       </c>
       <c r="V21" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W21" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X21" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y21" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W21" s="33" t="s">
+      <c r="Z21" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA21" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB21" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X21" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y21" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z21" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA21" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB21" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC21" s="33" t="s">
         <v>91</v>
@@ -7492,64 +7512,64 @@
         <v>91</v>
       </c>
       <c r="AF21" s="33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG21" s="33" t="s">
         <v>122</v>
       </c>
       <c r="AH21" s="33" t="s">
-        <v>378</v>
+        <v>686</v>
       </c>
       <c r="AI21" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>379</v>
+        <v>687</v>
       </c>
       <c r="AK21" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL21" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="AM21" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AN21" s="33" t="s">
-        <v>311</v>
+        <v>376</v>
+      </c>
+      <c r="AM21" s="33">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="33">
+        <v>3</v>
       </c>
       <c r="AO21" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP21" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ21" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR21" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS21" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT21" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU21" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV21" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW21" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU21" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV21" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW21" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX21" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY21" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ21" s="33" t="s">
         <v>108</v>
@@ -7558,30 +7578,30 @@
         <v>203</v>
       </c>
       <c r="BB21" s="33" t="s">
-        <v>109</v>
+        <v>638</v>
       </c>
       <c r="BC21" s="34" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="22" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:55" ht="62.1" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G22" s="33" t="s">
         <v>122</v>
@@ -7602,7 +7622,7 @@
         <v>91</v>
       </c>
       <c r="M22" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N22" s="33" t="s">
         <v>97</v>
@@ -7614,10 +7634,10 @@
         <v>91</v>
       </c>
       <c r="Q22" s="33" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="R22" s="33" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="S22" s="33" t="s">
         <v>91</v>
@@ -7626,28 +7646,28 @@
         <v>91</v>
       </c>
       <c r="U22" s="33" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="V22" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W22" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X22" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y22" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W22" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X22" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y22" s="33" t="s">
+      <c r="Z22" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z22" s="33" t="s">
+      <c r="AA22" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB22" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="AA22" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB22" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC22" s="33" t="s">
         <v>91</v>
@@ -7656,7 +7676,7 @@
         <v>60</v>
       </c>
       <c r="AE22" s="33" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AF22" s="33" t="s">
         <v>121</v>
@@ -7665,58 +7685,58 @@
         <v>122</v>
       </c>
       <c r="AH22" s="33" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AI22" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AK22" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL22" s="33" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AM22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR22" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS22" s="33" t="s">
         <v>127</v>
       </c>
       <c r="AT22" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU22" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV22" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW22" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU22" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV22" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW22" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX22" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY22" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ22" s="33" t="s">
         <v>108</v>
@@ -7728,30 +7748,30 @@
         <v>109</v>
       </c>
       <c r="BC22" s="34" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="23" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55" ht="62.1" customHeight="1">
       <c r="A23" s="32" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H23" s="33" t="s">
         <v>195</v>
@@ -7769,7 +7789,7 @@
         <v>91</v>
       </c>
       <c r="M23" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N23" s="33" t="s">
         <v>97</v>
@@ -7781,10 +7801,10 @@
         <v>91</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="R23" s="33" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="S23" s="33" t="s">
         <v>91</v>
@@ -7793,28 +7813,28 @@
         <v>91</v>
       </c>
       <c r="U23" s="33" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="V23" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W23" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X23" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y23" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W23" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X23" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y23" s="33" t="s">
+      <c r="Z23" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z23" s="33" t="s">
+      <c r="AA23" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB23" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="AA23" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB23" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC23" s="33" t="s">
         <v>91</v>
@@ -7823,67 +7843,67 @@
         <v>120</v>
       </c>
       <c r="AE23" s="33" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AF23" s="33" t="s">
         <v>121</v>
       </c>
       <c r="AG23" s="33" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AH23" s="33" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AI23" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AK23" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL23" s="33" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AM23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR23" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS23" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT23" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU23" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV23" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW23" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU23" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV23" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW23" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX23" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY23" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ23" s="33" t="s">
         <v>108</v>
@@ -7895,30 +7915,30 @@
         <v>109</v>
       </c>
       <c r="BC23" s="34" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="24" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55" ht="62.1" customHeight="1">
       <c r="A24" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="F24" s="33" t="s">
         <v>405</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="G24" s="33" t="s">
         <v>406</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>410</v>
       </c>
       <c r="H24" s="33" t="s">
         <v>221</v>
@@ -7936,7 +7956,7 @@
         <v>91</v>
       </c>
       <c r="M24" s="33" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="N24" s="33" t="s">
         <v>97</v>
@@ -7948,10 +7968,10 @@
         <v>91</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="R24" s="33" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="S24" s="33" t="s">
         <v>91</v>
@@ -7960,28 +7980,28 @@
         <v>91</v>
       </c>
       <c r="U24" s="33" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="V24" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W24" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X24" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W24" s="33" t="s">
+      <c r="Z24" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB24" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X24" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y24" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z24" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA24" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB24" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC24" s="33" t="s">
         <v>91</v>
@@ -7993,64 +8013,64 @@
         <v>91</v>
       </c>
       <c r="AF24" s="33" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AG24" s="33" t="s">
         <v>233</v>
       </c>
       <c r="AH24" s="33" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AI24" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ24" s="33" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AK24" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL24" s="33" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AM24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR24" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS24" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT24" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU24" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV24" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW24" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU24" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV24" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW24" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX24" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY24" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ24" s="33" t="s">
         <v>108</v>
@@ -8062,30 +8082,30 @@
         <v>109</v>
       </c>
       <c r="BC24" s="34" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+      <c r="A25" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="33" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="25" spans="1:55" ht="62.1" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="F25" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="B25" s="33" t="s">
-        <v>421</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>422</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>423</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>424</v>
-      </c>
       <c r="G25" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H25" s="33" t="s">
         <v>83</v>
@@ -8103,7 +8123,7 @@
         <v>91</v>
       </c>
       <c r="M25" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N25" s="33" t="s">
         <v>97</v>
@@ -8115,10 +8135,10 @@
         <v>91</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="R25" s="33" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="S25" s="33" t="s">
         <v>91</v>
@@ -8127,28 +8147,28 @@
         <v>91</v>
       </c>
       <c r="U25" s="33" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="V25" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W25" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X25" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y25" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W25" s="33" t="s">
+      <c r="Z25" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA25" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB25" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X25" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y25" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z25" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA25" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB25" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC25" s="33" t="s">
         <v>91</v>
@@ -8160,64 +8180,64 @@
         <v>91</v>
       </c>
       <c r="AF25" s="33" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AG25" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AH25" s="33" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AI25" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AK25" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL25" s="33" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AM25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR25" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS25" s="33" t="s">
         <v>105</v>
       </c>
       <c r="AT25" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU25" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV25" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW25" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU25" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV25" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW25" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX25" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY25" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ25" s="33" t="s">
         <v>108</v>
@@ -8226,30 +8246,30 @@
         <v>8</v>
       </c>
       <c r="BB25" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC25" s="34" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="26" spans="1:55" ht="62.1" customHeight="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A26" s="32" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="G26" s="33" t="s">
         <v>148</v>
@@ -8270,7 +8290,7 @@
         <v>91</v>
       </c>
       <c r="M26" s="33" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="N26" s="33" t="s">
         <v>97</v>
@@ -8282,10 +8302,10 @@
         <v>91</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="R26" s="33" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="S26" s="33" t="s">
         <v>91</v>
@@ -8294,25 +8314,25 @@
         <v>91</v>
       </c>
       <c r="U26" s="33" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="V26" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W26" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="X26" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y26" s="35" t="s">
         <v>97</v>
       </c>
       <c r="Z26" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA26" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AB26" s="35" t="s">
         <v>89</v>
@@ -8324,28 +8344,28 @@
         <v>180</v>
       </c>
       <c r="AE26" s="33" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AF26" s="33" t="s">
         <v>121</v>
       </c>
       <c r="AG26" s="33" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AH26" s="35" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AI26" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AK26" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL26" s="33" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AM26" s="33">
         <v>1</v>
@@ -8354,16 +8374,16 @@
         <v>2</v>
       </c>
       <c r="AO26" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP26" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ26" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR26" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS26" s="33" t="s">
         <v>127</v>
@@ -8372,19 +8392,19 @@
         <v>1</v>
       </c>
       <c r="AU26" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV26" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW26" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AV26" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW26" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX26" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY26" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AZ26" s="33" t="s">
         <v>108</v>
@@ -8393,30 +8413,30 @@
         <v>8</v>
       </c>
       <c r="BB26" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC26" s="36" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" ht="62.1" customHeight="1">
       <c r="A27" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>441</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>444</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>445</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>447</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>448</v>
       </c>
       <c r="G27" s="33" t="s">
         <v>180</v>
@@ -8437,7 +8457,7 @@
         <v>91</v>
       </c>
       <c r="M27" s="33" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="N27" s="33" t="s">
         <v>97</v>
@@ -8449,10 +8469,10 @@
         <v>91</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="R27" s="33" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="S27" s="33" t="s">
         <v>91</v>
@@ -8461,28 +8481,28 @@
         <v>91</v>
       </c>
       <c r="U27" s="33" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="V27" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W27" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X27" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y27" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W27" s="33" t="s">
+      <c r="Z27" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA27" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB27" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X27" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y27" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z27" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA27" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB27" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC27" s="33" t="s">
         <v>91</v>
@@ -8494,7 +8514,7 @@
         <v>91</v>
       </c>
       <c r="AF27" s="33" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG27" s="33" t="s">
         <v>180</v>
@@ -8503,55 +8523,55 @@
         <v>141</v>
       </c>
       <c r="AI27" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ27" s="33" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AK27" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL27" s="33" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AM27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR27" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS27" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT27" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU27" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV27" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW27" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU27" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV27" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW27" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX27" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY27" s="33" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AZ27" s="33" t="s">
         <v>108</v>
@@ -8563,30 +8583,30 @@
         <v>109</v>
       </c>
       <c r="BC27" s="34" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="28" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+      <c r="A28" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E28" s="33" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="28" spans="1:55" ht="62.1" customHeight="1">
-      <c r="A28" s="32" t="s">
+      <c r="F28" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="G28" s="33" t="s">
         <v>458</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>461</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="G28" s="33" t="s">
-        <v>462</v>
       </c>
       <c r="H28" s="33" t="s">
         <v>221</v>
@@ -8604,7 +8624,7 @@
         <v>91</v>
       </c>
       <c r="M28" s="35" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="N28" s="33" t="s">
         <v>97</v>
@@ -8616,10 +8636,10 @@
         <v>91</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="R28" s="33" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="S28" s="33" t="s">
         <v>91</v>
@@ -8628,28 +8648,28 @@
         <v>91</v>
       </c>
       <c r="U28" s="33" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="V28" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W28" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y28" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W28" s="33" t="s">
+      <c r="Z28" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA28" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB28" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X28" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y28" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z28" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA28" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB28" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC28" s="33" t="s">
         <v>91</v>
@@ -8667,19 +8687,19 @@
         <v>233</v>
       </c>
       <c r="AH28" s="33" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="AI28" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="AK28" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL28" s="33" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AM28" s="33">
         <v>6</v>
@@ -8688,37 +8708,37 @@
         <v>1</v>
       </c>
       <c r="AO28" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP28" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ28" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR28" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS28" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT28" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AU28" s="33">
         <v>0</v>
       </c>
       <c r="AV28" s="33" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AW28" s="33" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AX28" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY28" s="33" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AZ28" s="33" t="s">
         <v>108</v>
@@ -8727,30 +8747,30 @@
         <v>8</v>
       </c>
       <c r="BB28" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC28" s="34" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55" ht="62.1" customHeight="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A29" s="32" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>207</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>162</v>
@@ -8771,7 +8791,7 @@
         <v>91</v>
       </c>
       <c r="M29" s="35" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="N29" s="33" t="s">
         <v>97</v>
@@ -8783,109 +8803,109 @@
         <v>91</v>
       </c>
       <c r="Q29" s="33" t="s">
+        <v>472</v>
+      </c>
+      <c r="R29" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="S29" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T29" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U29" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="V29" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W29" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X29" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y29" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z29" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA29" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB29" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC29" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD29" s="35" t="s">
+        <v>663</v>
+      </c>
+      <c r="AE29" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="AF29" s="33" t="s">
         <v>476</v>
-      </c>
-      <c r="R29" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="S29" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T29" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U29" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="V29" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="W29" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X29" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y29" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z29" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA29" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB29" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="AC29" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD29" s="35" t="s">
-        <v>667</v>
-      </c>
-      <c r="AE29" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="AF29" s="33" t="s">
-        <v>480</v>
       </c>
       <c r="AG29" s="33" t="s">
         <v>162</v>
       </c>
       <c r="AH29" s="33" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AI29" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ29" s="35" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="AK29" s="35" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="AL29" s="33" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AM29" s="33">
         <v>6</v>
       </c>
       <c r="AN29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS29" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT29" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AU29" s="33">
         <v>1</v>
       </c>
       <c r="AV29" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW29" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AW29" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX29" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY29" s="33" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AZ29" s="33" t="s">
         <v>108</v>
@@ -8894,33 +8914,33 @@
         <v>8</v>
       </c>
       <c r="BB29" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC29" s="36" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55" ht="62.1" customHeight="1">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F30" s="33" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G30" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H30" s="33" t="s">
         <v>83</v>
@@ -8938,7 +8958,7 @@
         <v>91</v>
       </c>
       <c r="M30" s="33" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="N30" s="33" t="s">
         <v>97</v>
@@ -8950,10 +8970,10 @@
         <v>91</v>
       </c>
       <c r="Q30" s="33" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="R30" s="33" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="S30" s="33" t="s">
         <v>91</v>
@@ -8962,28 +8982,28 @@
         <v>91</v>
       </c>
       <c r="U30" s="33" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="V30" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W30" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X30" s="33" t="s">
+        <v>654</v>
+      </c>
+      <c r="Y30" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W30" s="33" t="s">
+      <c r="Z30" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA30" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB30" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X30" s="33" t="s">
-        <v>658</v>
-      </c>
-      <c r="Y30" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z30" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA30" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB30" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC30" s="33" t="s">
         <v>91</v>
@@ -8995,64 +9015,64 @@
         <v>91</v>
       </c>
       <c r="AF30" s="33" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AG30" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AH30" s="33" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AI30" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AK30" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL30" s="33" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AM30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR30" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS30" s="33" t="s">
         <v>105</v>
       </c>
       <c r="AT30" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU30" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV30" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="AW30" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU30" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV30" s="33" t="s">
-        <v>470</v>
-      </c>
-      <c r="AW30" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX30" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY30" s="33" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AZ30" s="33" t="s">
         <v>108</v>
@@ -9061,30 +9081,30 @@
         <v>8</v>
       </c>
       <c r="BB30" s="33" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="BC30" s="34" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55" ht="62.1" customHeight="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G31" s="33" t="s">
         <v>180</v>
@@ -9105,7 +9125,7 @@
         <v>91</v>
       </c>
       <c r="M31" s="33" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="N31" s="33" t="s">
         <v>97</v>
@@ -9117,10 +9137,10 @@
         <v>91</v>
       </c>
       <c r="Q31" s="33" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="R31" s="33" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="S31" s="33" t="s">
         <v>91</v>
@@ -9129,28 +9149,28 @@
         <v>91</v>
       </c>
       <c r="U31" s="33" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="V31" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W31" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X31" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y31" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W31" s="33" t="s">
+      <c r="Z31" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA31" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB31" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X31" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y31" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z31" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA31" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB31" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC31" s="33" t="s">
         <v>91</v>
@@ -9162,43 +9182,43 @@
         <v>91</v>
       </c>
       <c r="AF31" s="33" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG31" s="33" t="s">
         <v>180</v>
       </c>
       <c r="AH31" s="33" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="AI31" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ31" s="33" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="AK31" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL31" s="33" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AM31" s="33">
         <v>4</v>
       </c>
       <c r="AN31" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO31" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP31" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ31" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR31" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS31" s="33" t="s">
         <v>202</v>
@@ -9207,19 +9227,19 @@
         <v>0.75</v>
       </c>
       <c r="AU31" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV31" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW31" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AV31" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW31" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX31" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY31" s="33" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AZ31" s="33" t="s">
         <v>108</v>
@@ -9228,30 +9248,30 @@
         <v>8</v>
       </c>
       <c r="BB31" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC31" s="34" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55" ht="62.1" customHeight="1">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A32" s="32" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E32" s="33" t="s">
         <v>122</v>
       </c>
       <c r="F32" s="33" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G32" s="33" t="s">
         <v>122</v>
@@ -9272,7 +9292,7 @@
         <v>91</v>
       </c>
       <c r="M32" s="33" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="N32" s="33" t="s">
         <v>97</v>
@@ -9284,10 +9304,10 @@
         <v>91</v>
       </c>
       <c r="Q32" s="33" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="R32" s="33" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="S32" s="33" t="s">
         <v>91</v>
@@ -9296,28 +9316,28 @@
         <v>91</v>
       </c>
       <c r="U32" s="33" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="V32" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W32" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X32" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y32" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W32" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X32" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y32" s="33" t="s">
+      <c r="Z32" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z32" s="33" t="s">
-        <v>303</v>
-      </c>
       <c r="AA32" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AB32" s="33" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AC32" s="33" t="s">
         <v>91</v>
@@ -9326,67 +9346,67 @@
         <v>180</v>
       </c>
       <c r="AE32" s="33" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AF32" s="33" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AG32" s="33" t="s">
         <v>122</v>
       </c>
       <c r="AH32" s="33" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AI32" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AK32" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL32" s="33" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AM32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR32" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS32" s="33" t="s">
         <v>105</v>
       </c>
       <c r="AT32" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU32" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV32" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="AW32" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU32" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV32" s="33" t="s">
-        <v>470</v>
-      </c>
-      <c r="AW32" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX32" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY32" s="33" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AZ32" s="33" t="s">
         <v>108</v>
@@ -9395,33 +9415,33 @@
         <v>8</v>
       </c>
       <c r="BB32" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC32" s="34" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="33" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:55" ht="62.1" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H33" s="33" t="s">
         <v>221</v>
@@ -9439,7 +9459,7 @@
         <v>91</v>
       </c>
       <c r="M33" s="33" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="N33" s="33" t="s">
         <v>97</v>
@@ -9451,10 +9471,10 @@
         <v>91</v>
       </c>
       <c r="Q33" s="33" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="R33" s="33" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="S33" s="33" t="s">
         <v>91</v>
@@ -9463,28 +9483,28 @@
         <v>91</v>
       </c>
       <c r="U33" s="33" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="V33" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W33" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X33" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y33" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W33" s="33" t="s">
+      <c r="Z33" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA33" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB33" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X33" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y33" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z33" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA33" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB33" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC33" s="33" t="s">
         <v>91</v>
@@ -9502,58 +9522,58 @@
         <v>233</v>
       </c>
       <c r="AH33" s="33" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AI33" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AK33" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL33" s="33" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AM33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR33" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS33" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT33" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU33" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV33" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW33" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU33" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV33" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW33" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX33" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY33" s="33" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AZ33" s="33" t="s">
         <v>108</v>
@@ -9565,27 +9585,27 @@
         <v>109</v>
       </c>
       <c r="BC33" s="34" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="34" spans="1:55" ht="62.1" customHeight="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>207</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G34" s="33" t="s">
         <v>209</v>
@@ -9606,7 +9626,7 @@
         <v>91</v>
       </c>
       <c r="M34" s="33" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="N34" s="33" t="s">
         <v>97</v>
@@ -9618,10 +9638,10 @@
         <v>91</v>
       </c>
       <c r="Q34" s="33" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="R34" s="33" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="S34" s="33" t="s">
         <v>91</v>
@@ -9630,28 +9650,28 @@
         <v>91</v>
       </c>
       <c r="U34" s="33" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="V34" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W34" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X34" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y34" s="33" t="s">
+        <v>672</v>
+      </c>
+      <c r="Z34" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA34" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB34" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X34" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y34" s="33" t="s">
-        <v>676</v>
-      </c>
-      <c r="Z34" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA34" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB34" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC34" s="33" t="s">
         <v>91</v>
@@ -9663,43 +9683,43 @@
         <v>91</v>
       </c>
       <c r="AF34" s="33" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AG34" s="33" t="s">
         <v>209</v>
       </c>
       <c r="AH34" s="33" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AI34" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AK34" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL34" s="33" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AM34" s="33">
         <v>10</v>
       </c>
       <c r="AN34" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO34" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP34" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ34" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR34" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS34" s="33" t="s">
         <v>202</v>
@@ -9708,19 +9728,19 @@
         <v>0.75</v>
       </c>
       <c r="AU34" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV34" s="33" t="s">
+        <v>672</v>
+      </c>
+      <c r="AW34" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AV34" s="33" t="s">
-        <v>676</v>
-      </c>
-      <c r="AW34" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX34" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY34" s="33" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AZ34" s="33" t="s">
         <v>108</v>
@@ -9729,33 +9749,33 @@
         <v>8</v>
       </c>
       <c r="BB34" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC34" s="34" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="35" spans="1:55" ht="62.1" customHeight="1">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="35" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H35" s="33" t="s">
         <v>83</v>
@@ -9773,7 +9793,7 @@
         <v>91</v>
       </c>
       <c r="M35" s="33" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="N35" s="33" t="s">
         <v>97</v>
@@ -9785,10 +9805,10 @@
         <v>91</v>
       </c>
       <c r="Q35" s="33" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="R35" s="33" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="S35" s="33" t="s">
         <v>91</v>
@@ -9797,13 +9817,13 @@
         <v>91</v>
       </c>
       <c r="U35" s="33" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="V35" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W35" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="X35" s="35" t="s">
         <v>89</v>
@@ -9812,13 +9832,13 @@
         <v>97</v>
       </c>
       <c r="Z35" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA35" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB35" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="AA35" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB35" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC35" s="33" t="s">
         <v>91</v>
@@ -9830,64 +9850,64 @@
         <v>91</v>
       </c>
       <c r="AF35" s="33" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AG35" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AH35" s="33" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AI35" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AK35" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL35" s="33" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AM35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR35" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS35" s="33" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="AT35" s="33">
         <v>0.65</v>
       </c>
       <c r="AU35" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV35" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="AW35" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AV35" s="33" t="s">
-        <v>681</v>
-      </c>
-      <c r="AW35" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX35" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY35" s="33" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AZ35" s="33" t="s">
         <v>108</v>
@@ -9896,39 +9916,39 @@
         <v>8</v>
       </c>
       <c r="BB35" s="33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="BC35" s="34" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="36" spans="1:55" ht="62.1" customHeight="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E36" s="33" t="s">
         <v>207</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G36" s="33" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H36" s="33" t="s">
         <v>221</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J36" s="33" t="s">
         <v>91</v>
@@ -9940,7 +9960,7 @@
         <v>91</v>
       </c>
       <c r="M36" s="33" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="N36" s="33" t="s">
         <v>97</v>
@@ -9952,10 +9972,10 @@
         <v>91</v>
       </c>
       <c r="Q36" s="33" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="R36" s="33" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="S36" s="33" t="s">
         <v>91</v>
@@ -9964,28 +9984,28 @@
         <v>91</v>
       </c>
       <c r="U36" s="33" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="V36" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W36" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X36" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y36" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W36" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="X36" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y36" s="33" t="s">
+      <c r="Z36" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA36" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Z36" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA36" s="33" t="s">
+      <c r="AB36" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="AB36" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC36" s="33" t="s">
         <v>91</v>
@@ -9994,67 +10014,67 @@
         <v>169</v>
       </c>
       <c r="AE36" s="33" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AF36" s="33" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AG36" s="33" t="s">
         <v>162</v>
       </c>
       <c r="AH36" s="33" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AI36" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AK36" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL36" s="33" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AM36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR36" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS36" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT36" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU36" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV36" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW36" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="AU36" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV36" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW36" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="AX36" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY36" s="33" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AZ36" s="33" t="s">
         <v>108</v>
@@ -10063,33 +10083,33 @@
         <v>8</v>
       </c>
       <c r="BB36" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC36" s="34" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="37" spans="1:55" ht="62.1" customHeight="1">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="37" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A37" s="32" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E37" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="G37" s="33" t="s">
         <v>357</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>566</v>
-      </c>
-      <c r="G37" s="33" t="s">
-        <v>359</v>
       </c>
       <c r="H37" s="33" t="s">
         <v>195</v>
@@ -10107,7 +10127,7 @@
         <v>91</v>
       </c>
       <c r="M37" s="33" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N37" s="33" t="s">
         <v>97</v>
@@ -10119,10 +10139,10 @@
         <v>91</v>
       </c>
       <c r="Q37" s="33" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="R37" s="33" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="S37" s="33" t="s">
         <v>91</v>
@@ -10131,28 +10151,28 @@
         <v>91</v>
       </c>
       <c r="U37" s="33" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="V37" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W37" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="X37" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y37" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="W37" s="33" t="s">
+      <c r="Z37" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA37" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB37" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="X37" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y37" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z37" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA37" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB37" s="33" t="s">
-        <v>304</v>
       </c>
       <c r="AC37" s="33" t="s">
         <v>91</v>
@@ -10164,64 +10184,64 @@
         <v>91</v>
       </c>
       <c r="AF37" s="33" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG37" s="33" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AH37" s="33" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AI37" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AK37" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL37" s="33" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AM37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AQ37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AR37" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AS37" s="33" t="s">
         <v>202</v>
       </c>
       <c r="AT37" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU37" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV37" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW37" s="35" t="s">
         <v>311</v>
-      </c>
-      <c r="AU37" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AV37" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AW37" s="35" t="s">
-        <v>312</v>
       </c>
       <c r="AX37" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY37" s="33" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AZ37" s="33" t="s">
         <v>108</v>
@@ -10230,28 +10250,28 @@
         <v>8</v>
       </c>
       <c r="BB37" s="33" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="BC37" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A38" s="32"/>
       <c r="B38" s="35" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>122</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G38" s="33" t="s">
         <v>122</v>
@@ -10312,19 +10332,19 @@
     <row r="39" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A39" s="32"/>
       <c r="B39" s="35" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E39" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G39" s="33" t="s">
         <v>180</v>
@@ -10341,7 +10361,7 @@
       <c r="K39" s="35"/>
       <c r="L39" s="33"/>
       <c r="M39" s="35" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="N39" s="35" t="s">
         <v>97</v>
@@ -10365,7 +10385,7 @@
         <v>185</v>
       </c>
       <c r="U39" s="35" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="V39" s="33" t="s">
         <v>89</v>
@@ -10408,7 +10428,7 @@
       </c>
       <c r="AI39" s="33"/>
       <c r="AJ39" s="35" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="AK39" s="33" t="s">
         <v>187</v>
@@ -10447,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="AW39" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AX39" s="33" t="s">
         <v>89</v>
@@ -10460,10 +10480,10 @@
         <v>190</v>
       </c>
       <c r="BB39" s="33" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="BC39" s="36" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="40" spans="1:55" ht="62.1" hidden="1" customHeight="1">
@@ -10560,16 +10580,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27.95" customHeight="1">
@@ -10577,13 +10597,13 @@
         <v>78</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
@@ -10591,13 +10611,13 @@
         <v>78</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
@@ -10605,13 +10625,13 @@
         <v>78</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
@@ -10619,13 +10639,13 @@
         <v>78</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
@@ -10633,13 +10653,13 @@
         <v>78</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
@@ -10647,13 +10667,13 @@
         <v>111</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
@@ -10661,13 +10681,13 @@
         <v>111</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>116</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
@@ -10675,13 +10695,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
@@ -10689,13 +10709,13 @@
         <v>111</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
@@ -10703,13 +10723,13 @@
         <v>111</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
@@ -10717,13 +10737,13 @@
         <v>18</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
@@ -10731,13 +10751,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>134</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
@@ -10745,13 +10765,13 @@
         <v>18</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>135</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
@@ -10759,13 +10779,13 @@
         <v>18</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>586</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
@@ -10773,13 +10793,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
@@ -10787,13 +10807,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
@@ -10801,13 +10821,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>150</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
@@ -10815,13 +10835,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
@@ -10829,13 +10849,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>586</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
@@ -10843,13 +10863,13 @@
         <v>15</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
@@ -10857,13 +10877,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>165</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
@@ -10871,13 +10891,13 @@
         <v>9</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>165</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
@@ -10885,13 +10905,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
@@ -10899,13 +10919,13 @@
         <v>9</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>586</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
@@ -10913,13 +10933,13 @@
         <v>9</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
@@ -10927,13 +10947,13 @@
         <v>176</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
@@ -10941,13 +10961,13 @@
         <v>176</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>181</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
@@ -10955,13 +10975,13 @@
         <v>176</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
@@ -10969,13 +10989,13 @@
         <v>176</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
@@ -10983,13 +11003,13 @@
         <v>176</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>182</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
@@ -10997,13 +11017,13 @@
         <v>192</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
@@ -11011,13 +11031,13 @@
         <v>192</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>116</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
@@ -11025,13 +11045,13 @@
         <v>192</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
@@ -11039,13 +11059,13 @@
         <v>192</v>
       </c>
       <c r="B35" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>586</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="27.95" customHeight="1">
@@ -11053,13 +11073,13 @@
         <v>192</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="27.95" customHeight="1">
@@ -11067,13 +11087,13 @@
         <v>205</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27.95" customHeight="1">
@@ -11081,13 +11101,13 @@
         <v>205</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="27.95" customHeight="1">
@@ -11095,13 +11115,13 @@
         <v>205</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27.95" customHeight="1">
@@ -11109,13 +11129,13 @@
         <v>205</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>211</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="27.95" customHeight="1">
@@ -11123,13 +11143,13 @@
         <v>205</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>212</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.95" customHeight="1">
@@ -11137,13 +11157,13 @@
         <v>12</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="27.95" customHeight="1">
@@ -11151,13 +11171,13 @@
         <v>12</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="27.95" customHeight="1">
@@ -11165,13 +11185,13 @@
         <v>12</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="27.95" customHeight="1">
@@ -11179,13 +11199,13 @@
         <v>12</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>223</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="27.95" customHeight="1">
@@ -11193,13 +11213,13 @@
         <v>12</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="27.95" customHeight="1">
@@ -11207,13 +11227,13 @@
         <v>230</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>234</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="27.95" customHeight="1">
@@ -11221,13 +11241,13 @@
         <v>230</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>235</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="27.95" customHeight="1">
@@ -11235,13 +11255,13 @@
         <v>230</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="27.95" customHeight="1">
@@ -11249,13 +11269,13 @@
         <v>230</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="27.95" customHeight="1">
@@ -11263,909 +11283,909 @@
         <v>230</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>236</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="27.95" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="27.95" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="27.95" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="27.95" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="27.95" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="27.95" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.95" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27.95" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="27.95" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27.95" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="27.95" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="27.95" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="27.95" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27.95" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27.95" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="27.95" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="27.95" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="27.95" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="27.95" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>211</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="27.95" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="27.95" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="27.95" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="27.95" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="27.95" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="27.95" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="27.95" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B77" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="27.95" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="27.95" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B79" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="27.95" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="27.95" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B81" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="27.95" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="27.95" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B83" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="27.95" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="27.95" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B85" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="27.95" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="27.95" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="27.95" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="27.95" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="27.95" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="27.95" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B91" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="27.95" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="27.95" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="27.95" customHeight="1">
       <c r="A94" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C94" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>449</v>
-      </c>
       <c r="D94" s="16" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="27.95" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="27.95" customHeight="1">
       <c r="A96" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C96" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>463</v>
-      </c>
       <c r="D96" s="16" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="27.95" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="27.95" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="27.95" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B99" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="27.95" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="27.95" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B101" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="27.95" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="27.95" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B103" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="27.95" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="27.95" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="27.95" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="27.95" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="27.95" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="27.95" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B109" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="27.95" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="27.95" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="27.95" customHeight="1">
       <c r="A112" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C112" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="B112" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>553</v>
-      </c>
       <c r="D112" s="16" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="27.95" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="27.95" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="27.95" customHeight="1">
       <c r="A115" s="17" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>38</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -12189,7 +12209,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="40" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -12203,86 +12223,86 @@
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="20" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="44.1" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="44.1" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="44.1" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="44.1" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="44.1" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="44.1" customHeight="1">
@@ -12290,27 +12310,27 @@
         <v>75</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="44.1" customHeight="1">
       <c r="A11" s="23" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="44.1" customHeight="1">
@@ -12318,13 +12338,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="44.1" customHeight="1">
@@ -12332,13 +12352,13 @@
         <v>203</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="44.1" customHeight="1">
@@ -12346,27 +12366,27 @@
         <v>190</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="44.1" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BlueFox_CUO_Audit_Consolidation.xlsx
+++ b/docs/BlueFox_CUO_Audit_Consolidation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\Minijeu Yllias\V3_BlueFox odyssey Fondation IA\V3_EXECUTABL_fondation IA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F73673F-6D5F-441A-9550-9AFCC684C398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D60C6A-1EEB-4E5B-A107-1BA0EC78E89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5295" yWindow="1755" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="723">
   <si>
     <t>BlueFox Odyssey — CUO documentaire consolidé</t>
   </si>
@@ -1196,9 +1196,6 @@
     <t>fluorescent_biomass</t>
   </si>
   <si>
-    <t>botany · bioluminescence</t>
-  </si>
-  <si>
     <t>Étude de la flore · récolte biologique · balisage nocturne</t>
   </si>
   <si>
@@ -1217,9 +1214,6 @@
     <t>giant_alien_fungus</t>
   </si>
   <si>
-    <t>fungus</t>
-  </si>
-  <si>
     <t>Colonie fongique · arche de sporophores</t>
   </si>
   <si>
@@ -1232,12 +1226,6 @@
     <t>fungal_sample</t>
   </si>
   <si>
-    <t>mycology · biology · toxins</t>
-  </si>
-  <si>
-    <t>Étude fongique · prélèvement prudent · risque environnemental</t>
-  </si>
-  <si>
     <t>decor · fungus · spore · biological · landmark</t>
   </si>
   <si>
@@ -1283,9 +1271,6 @@
     <t>environment · liquid · corridor · phenomenon</t>
   </si>
   <si>
-    <t>Décor environnemental — comportement et franchissement à valider</t>
-  </si>
-  <si>
     <t>DOC-FAU-NOCT-M-001</t>
   </si>
   <si>
@@ -1977,9 +1962,6 @@
   </si>
   <si>
     <t>Reconnaissance du terrain · cartographie · indices géologiques - Possible — événements génériques, aucun objectif dédié</t>
-  </si>
-  <si>
-    <t>— constructeur + population de carte+  séparateurs bordures</t>
   </si>
   <si>
     <t>À corriger</t>
@@ -2101,6 +2083,129 @@
   </si>
   <si>
     <t>Identifier une espèce · signature énergétique · cartographie de biome - compréhension du monde mineral</t>
+  </si>
+  <si>
+    <t>botany · bioluminescence - energy</t>
+  </si>
+  <si>
+    <t>forest · jungle · swamp · mushroom</t>
+  </si>
+  <si>
+    <t>mycology · biology · research + food</t>
+  </si>
+  <si>
+    <t>Étude fongique · prélèvement prudent · risque environnemental  découverte d'une source d'alimentation rxtremement riche</t>
+  </si>
+  <si>
+    <t>Ressource/décor — intégration autorisable après validation du tableau - récolte +transformation à la base donne les 10 prochaines rations qui régénèrent l'energie à 100% et ralentissent le niveau de fatigue</t>
+  </si>
+  <si>
+    <t>Décor environnemental — comportement à valider et franchissement possible avec le texte de bluefox "Juste assez profond pour me rafraichir les coussinets" ou "Ce filet d'eau me rafraichit les pattes"</t>
+  </si>
+  <si>
+    <t>desert · volcanic - magnetic</t>
+  </si>
+  <si>
+    <t>traversée de la brume réduit l'energie de 10%</t>
+  </si>
+  <si>
+    <t>Strong_rock</t>
+  </si>
+  <si>
+    <t>Roche solide</t>
+  </si>
+  <si>
+    <t>solid_rock</t>
+  </si>
+  <si>
+    <t>Éboulis · balisage naturel · abri minéral - obstacle</t>
+  </si>
+  <si>
+    <t>constructeur + population de carte + propositions explicites</t>
+  </si>
+  <si>
+    <t>— constructeur + population de carte+  séparateurs bordures. Forme saillantes et découpées, éviter les arrondis</t>
+  </si>
+  <si>
+    <t>plaines - foret - swamp - Tous les biomes sauf desert, , glace et volcanique</t>
+  </si>
+  <si>
+    <t>default · forest · jungle · swamp · ruins · desert · mountain · cave · coast · tundra - plaine · volcanic · frozen · aquatic · crystalline · alien</t>
+  </si>
+  <si>
+    <t>tree_fallen</t>
+  </si>
+  <si>
+    <t>Branche</t>
+  </si>
+  <si>
+    <t>ressource</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>default · forest · jungle · swamp - mushroom - plaine - desert</t>
+  </si>
+  <si>
+    <t>Bosquet  d'arbres : 2 arbres différents, un buisson et 1 à 2 branches</t>
+  </si>
+  <si>
+    <t>harvests</t>
+  </si>
+  <si>
+    <t>présent · repéré · observé · cartographié · altéré - transformé : planche/bois - brulé</t>
+  </si>
+  <si>
+    <t>observe - transforme  brule</t>
+  </si>
+  <si>
+    <t>harvestable - transformable : bois de construction - conbustible  : feu pour le camp</t>
+  </si>
+  <si>
+    <t>x5 brut Nécessaire pour le camp : feu de bois /x15 transformé en bois de constructoin nécessaires pour un refuge</t>
+  </si>
+  <si>
+    <t>Étude de la flore · habitat - x5 brut Nécessaire pour le camp : feu de bois /x15 transformé en bois de constructoin nécessaires pour un refuge</t>
+  </si>
+  <si>
+    <t>déclencheur mission : observation : "peut servir pour fabriquer un refuge si je la transforme un peu"</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Crucial pour fabriquer les refuges. 5crystaux + une branche -&gt; bois de construction -&gt; planche pour construir le refuge</t>
+  </si>
+  <si>
+    <t>1 arbre 1 rocher 1 à 3 buissons  1 plante médium et 2 small</t>
+  </si>
+  <si>
+    <t>présente · identifiée · analysée · récoltée · régénération transformée</t>
+  </si>
+  <si>
+    <t>observe · inspect · analyze · collect  transform</t>
+  </si>
+  <si>
+    <t>combustible  transformable</t>
+  </si>
+  <si>
+    <t>flora  - engineering</t>
+  </si>
+  <si>
+    <t>camp - construction refuge</t>
+  </si>
+  <si>
+    <t>OBJECT_SEEN · OBJECT_INSPECTED ·collecter - transformer</t>
+  </si>
+  <si>
+    <t>ressource bois</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> feu/camp : x5 bush; fabriquer les refuges. 6  crystaux + 2 bush -&gt; bois de construction -&gt; planche pour construir le refuge</t>
   </si>
 </sst>
 </file>
@@ -2491,7 +2596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2607,6 +2712,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3541,14 +3647,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CUO_Master_Table" displayName="CUO_Master_Table" ref="A1:BC40" totalsRowShown="0">
-  <autoFilter ref="A1:BC40" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="52">
-      <filters>
-        <filter val="P2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CUO_Master_Table" displayName="CUO_Master_Table" ref="A1:BC42" totalsRowShown="0">
+  <autoFilter ref="A1:BC42" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="55">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID CUO" dataDxfId="58"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type technique" dataDxfId="57"/>
@@ -3907,8 +4007,8 @@
         <v>7</v>
       </c>
       <c r="B7" s="7">
-        <f>COUNTA(CUO_Master!$A$2:$A$40)</f>
-        <v>36</v>
+        <f>COUNTA(CUO_Master!$A$2:$A$42)</f>
+        <v>38</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="8" t="s">
@@ -3928,8 +4028,8 @@
         <v>11</v>
       </c>
       <c r="B8" s="9">
-        <f>COUNTIF(CUO_Master!$AX$2:$AX$40,"Oui")</f>
-        <v>15</v>
+        <f>COUNTIF(CUO_Master!$AX$2:$AX$42,"Oui")</f>
+        <v>16</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="8" t="s">
@@ -3949,8 +4049,8 @@
         <v>14</v>
       </c>
       <c r="B9" s="9">
-        <f>COUNTIF(CUO_Master!$D$2:$D$40,"documentary")</f>
-        <v>24</v>
+        <f>COUNTIF(CUO_Master!$D$2:$D$42,"documentary")</f>
+        <v>26</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="8" t="s">
@@ -3970,7 +4070,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="9">
-        <f>COUNTIF(CUO_Master!$N$2:$N$40,"Oui")</f>
+        <f>COUNTIF(CUO_Master!$N$2:$N$42,"Oui")</f>
         <v>10</v>
       </c>
       <c r="C10" s="4"/>
@@ -3991,8 +4091,8 @@
         <v>20</v>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(CUO_Master!$BB$2:$BB$40,"Validé")</f>
-        <v>8</v>
+        <f>COUNTIF(CUO_Master!$BB$2:$BB$42,"Validé")</f>
+        <v>14</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -4045,7 +4145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BC40"/>
+  <dimension ref="A1:BC42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="1.125" customWidth="1"/>
@@ -4264,7 +4364,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="2" spans="1:55" ht="62.1" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>77</v>
       </c>
@@ -4425,11 +4525,11 @@
         <v>8</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC2" s="31"/>
     </row>
-    <row r="3" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="3" spans="1:55" ht="62.1" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>110</v>
       </c>
@@ -4590,11 +4690,11 @@
         <v>8</v>
       </c>
       <c r="BB3" s="33" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC3" s="34"/>
     </row>
-    <row r="4" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="4" spans="1:55" ht="62.1" customHeight="1">
       <c r="A4" s="32" t="s">
         <v>128</v>
       </c>
@@ -4755,11 +4855,11 @@
         <v>8</v>
       </c>
       <c r="BB4" s="33" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC4" s="34"/>
     </row>
-    <row r="5" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="5" spans="1:55" ht="62.1" customHeight="1">
       <c r="A5" s="32" t="s">
         <v>145</v>
       </c>
@@ -4860,13 +4960,13 @@
         <v>122</v>
       </c>
       <c r="AH5" s="35" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="AI5" s="33" t="s">
         <v>158</v>
       </c>
       <c r="AJ5" s="35" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="AK5" s="33" t="s">
         <v>103</v>
@@ -4924,7 +5024,7 @@
       </c>
       <c r="BC5" s="34"/>
     </row>
-    <row r="6" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="6" spans="1:55" ht="62.1" customHeight="1">
       <c r="A6" s="32" t="s">
         <v>160</v>
       </c>
@@ -5085,13 +5185,13 @@
         <v>8</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="BC6" s="36" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55" ht="62.1" customHeight="1">
       <c r="A7" s="32" t="s">
         <v>175</v>
       </c>
@@ -5129,7 +5229,7 @@
         <v>87</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>88</v>
+        <v>697</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>89</v>
@@ -5171,7 +5271,7 @@
         <v>89</v>
       </c>
       <c r="AA7" s="33" t="s">
-        <v>96</v>
+        <v>666</v>
       </c>
       <c r="AB7" s="33" t="s">
         <v>97</v>
@@ -5252,7 +5352,7 @@
         <v>190</v>
       </c>
       <c r="BB7" s="33" t="s">
-        <v>109</v>
+        <v>633</v>
       </c>
       <c r="BC7" s="34"/>
     </row>
@@ -5336,7 +5436,7 @@
         <v>89</v>
       </c>
       <c r="AA8" s="33" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="AB8" s="33" t="s">
         <v>97</v>
@@ -5357,7 +5457,7 @@
         <v>122</v>
       </c>
       <c r="AH8" s="33" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="AI8" s="33" t="s">
         <v>158</v>
@@ -5417,11 +5517,11 @@
         <v>203</v>
       </c>
       <c r="BB8" s="33" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC8" s="34"/>
     </row>
-    <row r="9" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="9" spans="1:55" ht="62.1" customHeight="1">
       <c r="A9" s="32" t="s">
         <v>204</v>
       </c>
@@ -5582,13 +5682,13 @@
         <v>8</v>
       </c>
       <c r="BB9" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="BC9" s="34" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="10" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" ht="62.1" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>218</v>
       </c>
@@ -5650,7 +5750,7 @@
         <v>91</v>
       </c>
       <c r="U10" s="35" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="V10" s="33" t="s">
         <v>97</v>
@@ -5749,10 +5849,10 @@
         <v>8</v>
       </c>
       <c r="BB10" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="BC10" s="36" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:55" ht="62.1" customHeight="1">
@@ -5826,7 +5926,7 @@
         <v>97</v>
       </c>
       <c r="X11" s="33" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="Y11" s="33" t="s">
         <v>97</v>
@@ -5835,7 +5935,7 @@
         <v>97</v>
       </c>
       <c r="AA11" s="33" t="s">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="AB11" s="33" t="s">
         <v>97</v>
@@ -5856,7 +5956,7 @@
         <v>233</v>
       </c>
       <c r="AH11" s="33" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="AI11" s="33" t="s">
         <v>142</v>
@@ -5916,13 +6016,13 @@
         <v>203</v>
       </c>
       <c r="BB11" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="BC11" s="34" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="12" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55" ht="62.1" customHeight="1">
       <c r="A12" s="32" t="s">
         <v>241</v>
       </c>
@@ -5987,13 +6087,13 @@
         <v>251</v>
       </c>
       <c r="V12" s="33" t="s">
-        <v>97</v>
+        <v>648</v>
       </c>
       <c r="W12" s="33" t="s">
         <v>97</v>
       </c>
       <c r="X12" s="33" t="s">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="Y12" s="33" t="s">
         <v>97</v>
@@ -6083,94 +6183,88 @@
         <v>190</v>
       </c>
       <c r="BB12" s="33" t="s">
-        <v>109</v>
+        <v>633</v>
       </c>
       <c r="BC12" s="34"/>
     </row>
-    <row r="13" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="13" spans="1:55" ht="62.1" customHeight="1">
       <c r="A13" s="32" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>256</v>
+        <v>690</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>257</v>
+        <v>691</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>178</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>258</v>
+        <v>692</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="I13" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="33" t="s">
-        <v>259</v>
-      </c>
+      <c r="J13" s="33"/>
       <c r="K13" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>261</v>
+        <v>181</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>87</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>262</v>
+        <v>88</v>
       </c>
       <c r="N13" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33" t="s">
+        <v>693</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="U13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="V13" s="33" t="s">
         <v>89</v>
-      </c>
-      <c r="O13" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="P13" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q13" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="R13" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="S13" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T13" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="U13" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="V13" s="33" t="s">
-        <v>97</v>
       </c>
       <c r="W13" s="33" t="s">
         <v>97</v>
       </c>
       <c r="X13" s="33" t="s">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="Y13" s="33" t="s">
         <v>97</v>
       </c>
       <c r="Z13" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA13" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="AB13" s="33" t="s">
         <v>97</v>
-      </c>
-      <c r="AA13" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB13" s="33" t="s">
-        <v>96</v>
       </c>
       <c r="AC13" s="33" t="s">
         <v>91</v>
@@ -6185,46 +6279,46 @@
         <v>91</v>
       </c>
       <c r="AG13" s="33" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="AH13" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AI13" s="33" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="AJ13" s="33" t="s">
-        <v>266</v>
+        <v>186</v>
       </c>
       <c r="AK13" s="33" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="AL13" s="33" t="s">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="AM13" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN13" s="33">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AO13" s="33">
-        <v>0.55000000000000004</v>
+        <v>1.3</v>
       </c>
       <c r="AP13" s="33">
         <v>0</v>
       </c>
       <c r="AQ13" s="33">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AR13" s="33">
-        <v>0.42</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AS13" s="33" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="AT13" s="33">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="33">
         <v>0</v>
@@ -6232,8 +6326,8 @@
       <c r="AV13" s="33">
         <v>0</v>
       </c>
-      <c r="AW13" s="33" t="s">
-        <v>106</v>
+      <c r="AW13" s="35" t="s">
+        <v>311</v>
       </c>
       <c r="AX13" s="33" t="s">
         <v>89</v>
@@ -6248,19 +6342,21 @@
         <v>190</v>
       </c>
       <c r="BB13" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="BC13" s="34"/>
+        <v>633</v>
+      </c>
+      <c r="BC13" s="34" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="14" spans="1:55" ht="62.1" customHeight="1">
       <c r="A14" s="32" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>80</v>
@@ -6269,7 +6365,7 @@
         <v>178</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="G14" s="33" t="s">
         <v>178</v>
@@ -6278,19 +6374,19 @@
         <v>114</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>637</v>
+        <v>84</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>259</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="L14" s="33" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="N14" s="33" t="s">
         <v>89</v>
@@ -6299,13 +6395,13 @@
         <v>118</v>
       </c>
       <c r="P14" s="33" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="Q14" s="33" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="R14" s="33" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="S14" s="33" t="s">
         <v>91</v>
@@ -6317,13 +6413,13 @@
         <v>251</v>
       </c>
       <c r="V14" s="33" t="s">
-        <v>97</v>
+        <v>648</v>
       </c>
       <c r="W14" s="33" t="s">
         <v>97</v>
       </c>
       <c r="X14" s="33" t="s">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="Y14" s="33" t="s">
         <v>97</v>
@@ -6332,10 +6428,10 @@
         <v>97</v>
       </c>
       <c r="AA14" s="33" t="s">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="AB14" s="33" t="s">
-        <v>96</v>
+        <v>666</v>
       </c>
       <c r="AC14" s="33" t="s">
         <v>91</v>
@@ -6359,37 +6455,37 @@
         <v>158</v>
       </c>
       <c r="AJ14" s="33" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="AK14" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AL14" s="33" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="AM14" s="33">
         <v>1</v>
       </c>
       <c r="AN14" s="33">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AO14" s="33">
-        <v>0.8</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AP14" s="33">
         <v>0</v>
       </c>
       <c r="AQ14" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AR14" s="33">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AS14" s="33" t="s">
         <v>127</v>
       </c>
       <c r="AT14" s="33">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="AU14" s="33">
         <v>0</v>
@@ -6407,70 +6503,70 @@
         <v>107</v>
       </c>
       <c r="AZ14" s="33" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="BA14" s="33" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="BB14" s="33" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC14" s="34"/>
     </row>
     <row r="15" spans="1:55" ht="62.1" customHeight="1">
       <c r="A15" s="32" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>114</v>
       </c>
       <c r="I15" s="33" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>222</v>
+        <v>632</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="L15" s="33" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="N15" s="33" t="s">
         <v>89</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="P15" s="33" t="s">
-        <v>287</v>
+        <v>151</v>
       </c>
       <c r="Q15" s="33" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="R15" s="33" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="S15" s="33" t="s">
         <v>91</v>
@@ -6521,40 +6617,40 @@
         <v>91</v>
       </c>
       <c r="AI15" s="33" t="s">
-        <v>252</v>
+        <v>158</v>
       </c>
       <c r="AJ15" s="33" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="AK15" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AL15" s="33" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AM15" s="33">
         <v>1</v>
       </c>
       <c r="AN15" s="33">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO15" s="33">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP15" s="33">
         <v>0</v>
       </c>
       <c r="AQ15" s="33">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AR15" s="33">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="AS15" s="33" t="s">
         <v>127</v>
       </c>
       <c r="AT15" s="33">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="AU15" s="33">
         <v>0</v>
@@ -6578,201 +6674,199 @@
         <v>203</v>
       </c>
       <c r="BB15" s="33" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="BC15" s="34"/>
     </row>
-    <row r="16" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="16" spans="1:55" ht="62.1" customHeight="1">
       <c r="A16" s="32" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="I16" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>222</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>91</v>
+        <v>284</v>
       </c>
       <c r="L16" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="M16" s="35" t="s">
-        <v>655</v>
+        <v>285</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>286</v>
       </c>
       <c r="N16" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="O16" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="P16" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q16" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="R16" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="S16" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T16" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U16" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="V16" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="O16" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q16" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="R16" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="S16" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="T16" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="U16" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="V16" s="33" t="s">
-        <v>300</v>
-      </c>
       <c r="W16" s="33" t="s">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="X16" s="33" t="s">
-        <v>300</v>
+        <v>96</v>
       </c>
       <c r="Y16" s="33" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="Z16" s="33" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="AA16" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB16" s="35" t="s">
-        <v>654</v>
+        <v>96</v>
+      </c>
+      <c r="AB16" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="AC16" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD16" s="33">
-        <v>90</v>
+      <c r="AD16" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="AE16" s="33" t="s">
-        <v>304</v>
+        <v>91</v>
       </c>
       <c r="AF16" s="33" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG16" s="33" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AH16" s="33" t="s">
-        <v>305</v>
+        <v>91</v>
       </c>
       <c r="AI16" s="33" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AK16" s="33" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
       <c r="AL16" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="AM16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AO16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AP16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR16" s="33" t="s">
-        <v>310</v>
+        <v>291</v>
+      </c>
+      <c r="AM16" s="33">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="33">
+        <v>16</v>
+      </c>
+      <c r="AO16" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="AP16" s="33">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="33">
+        <v>36</v>
+      </c>
+      <c r="AR16" s="33">
+        <v>0.72</v>
       </c>
       <c r="AS16" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="AT16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AU16" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AV16" s="33" t="s">
-        <v>310</v>
+        <v>127</v>
+      </c>
+      <c r="AT16" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="AU16" s="33">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="33">
+        <v>0</v>
       </c>
       <c r="AW16" s="33" t="s">
-        <v>311</v>
+        <v>106</v>
       </c>
       <c r="AX16" s="33" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AY16" s="33" t="s">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="AZ16" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA16" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB16" s="33" t="s">
-        <v>653</v>
-      </c>
-      <c r="BC16" s="36" t="s">
-        <v>659</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="BC16" s="34"/>
     </row>
     <row r="17" spans="1:55" ht="62.1" customHeight="1">
       <c r="A17" s="32" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>122</v>
+        <v>293</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>78</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="I17" s="33" t="s">
         <v>132</v>
@@ -6786,8 +6880,8 @@
       <c r="L17" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="M17" s="33" t="s">
-        <v>683</v>
+      <c r="M17" s="35" t="s">
+        <v>649</v>
       </c>
       <c r="N17" s="33" t="s">
         <v>97</v>
@@ -6799,25 +6893,25 @@
         <v>91</v>
       </c>
       <c r="Q17" s="33" t="s">
-        <v>684</v>
+        <v>297</v>
       </c>
       <c r="R17" s="33" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="S17" s="33" t="s">
         <v>91</v>
       </c>
       <c r="T17" s="33" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="U17" s="33" t="s">
-        <v>168</v>
+        <v>299</v>
       </c>
       <c r="V17" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W17" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X17" s="33" t="s">
         <v>300</v>
@@ -6831,44 +6925,44 @@
       <c r="AA17" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="AB17" s="33" t="s">
-        <v>303</v>
+      <c r="AB17" s="35" t="s">
+        <v>648</v>
       </c>
       <c r="AC17" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD17" s="33" t="s">
-        <v>169</v>
+      <c r="AD17" s="33">
+        <v>90</v>
       </c>
       <c r="AE17" s="33" t="s">
-        <v>91</v>
+        <v>304</v>
       </c>
       <c r="AF17" s="33" t="s">
-        <v>321</v>
+        <v>98</v>
       </c>
       <c r="AG17" s="33" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="AH17" s="33" t="s">
-        <v>681</v>
+        <v>305</v>
       </c>
       <c r="AI17" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="AK17" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL17" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="AM17" s="33">
-        <v>3</v>
-      </c>
-      <c r="AN17" s="33">
-        <v>5</v>
+        <v>309</v>
+      </c>
+      <c r="AM17" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN17" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AO17" s="33" t="s">
         <v>310</v>
@@ -6883,7 +6977,7 @@
         <v>310</v>
       </c>
       <c r="AS17" s="33" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="AT17" s="33" t="s">
         <v>310</v>
@@ -6901,48 +6995,48 @@
         <v>97</v>
       </c>
       <c r="AY17" s="33" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AZ17" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA17" s="33" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
       <c r="BB17" s="33" t="s">
-        <v>648</v>
-      </c>
-      <c r="BC17" s="34" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="18" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>647</v>
+      </c>
+      <c r="BC17" s="36" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" ht="62.1" customHeight="1">
       <c r="A18" s="32" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>328</v>
+        <v>178</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>328</v>
+        <v>317</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>122</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J18" s="33" t="s">
         <v>91</v>
@@ -6954,7 +7048,7 @@
         <v>91</v>
       </c>
       <c r="M18" s="33" t="s">
-        <v>330</v>
+        <v>677</v>
       </c>
       <c r="N18" s="33" t="s">
         <v>97</v>
@@ -6966,10 +7060,10 @@
         <v>91</v>
       </c>
       <c r="Q18" s="33" t="s">
-        <v>331</v>
+        <v>678</v>
       </c>
       <c r="R18" s="33" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="S18" s="33" t="s">
         <v>91</v>
@@ -6978,7 +7072,7 @@
         <v>91</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="V18" s="33" t="s">
         <v>300</v>
@@ -7008,34 +7102,34 @@
         <v>169</v>
       </c>
       <c r="AE18" s="33" t="s">
-        <v>326</v>
+        <v>91</v>
       </c>
       <c r="AF18" s="33" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AG18" s="33" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="AH18" s="33" t="s">
-        <v>334</v>
+        <v>675</v>
       </c>
       <c r="AI18" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ18" s="33" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="AK18" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL18" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="AM18" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN18" s="33" t="s">
-        <v>310</v>
+        <v>323</v>
+      </c>
+      <c r="AM18" s="33">
+        <v>3</v>
+      </c>
+      <c r="AN18" s="33">
+        <v>5</v>
       </c>
       <c r="AO18" s="33" t="s">
         <v>310</v>
@@ -7050,7 +7144,7 @@
         <v>310</v>
       </c>
       <c r="AS18" s="33" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="AT18" s="33" t="s">
         <v>310</v>
@@ -7074,42 +7168,42 @@
         <v>108</v>
       </c>
       <c r="BA18" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB18" s="33" t="s">
-        <v>648</v>
-      </c>
-      <c r="BC18" s="36" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="19" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>642</v>
+      </c>
+      <c r="BC18" s="34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:55" ht="62.1" customHeight="1">
       <c r="A19" s="32" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>162</v>
+        <v>328</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="I19" s="33" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="J19" s="33" t="s">
         <v>91</v>
@@ -7121,7 +7215,7 @@
         <v>91</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="N19" s="33" t="s">
         <v>97</v>
@@ -7133,10 +7227,10 @@
         <v>91</v>
       </c>
       <c r="Q19" s="33" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="R19" s="33" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="S19" s="33" t="s">
         <v>91</v>
@@ -7145,13 +7239,13 @@
         <v>91</v>
       </c>
       <c r="U19" s="33" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="V19" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W19" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X19" s="33" t="s">
         <v>300</v>
@@ -7175,28 +7269,28 @@
         <v>169</v>
       </c>
       <c r="AE19" s="33" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="AF19" s="33" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="AG19" s="33" t="s">
         <v>162</v>
       </c>
       <c r="AH19" s="33" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="AI19" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="AK19" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL19" s="33" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="AM19" s="33" t="s">
         <v>310</v>
@@ -7217,7 +7311,7 @@
         <v>310</v>
       </c>
       <c r="AS19" s="33" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="AT19" s="33" t="s">
         <v>310</v>
@@ -7244,39 +7338,39 @@
         <v>8</v>
       </c>
       <c r="BB19" s="33" t="s">
-        <v>653</v>
-      </c>
-      <c r="BC19" s="34" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="20" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>642</v>
+      </c>
+      <c r="BC19" s="36" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="20" spans="1:55" ht="62.1" customHeight="1">
       <c r="A20" s="32" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="D20" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>357</v>
+        <v>162</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="J20" s="33" t="s">
         <v>91</v>
@@ -7288,7 +7382,7 @@
         <v>91</v>
       </c>
       <c r="M20" s="33" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="N20" s="33" t="s">
         <v>97</v>
@@ -7300,10 +7394,10 @@
         <v>91</v>
       </c>
       <c r="Q20" s="33" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="R20" s="33" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="S20" s="33" t="s">
         <v>91</v>
@@ -7312,13 +7406,13 @@
         <v>91</v>
       </c>
       <c r="U20" s="33" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="V20" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W20" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X20" s="33" t="s">
         <v>300</v>
@@ -7327,7 +7421,7 @@
         <v>301</v>
       </c>
       <c r="Z20" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA20" s="33" t="s">
         <v>302</v>
@@ -7342,28 +7436,28 @@
         <v>169</v>
       </c>
       <c r="AE20" s="33" t="s">
-        <v>91</v>
+        <v>346</v>
       </c>
       <c r="AF20" s="33" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="AG20" s="33" t="s">
-        <v>357</v>
+        <v>162</v>
       </c>
       <c r="AH20" s="33" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AI20" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ20" s="33" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="AK20" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL20" s="33" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="AM20" s="33" t="s">
         <v>310</v>
@@ -7384,7 +7478,7 @@
         <v>310</v>
       </c>
       <c r="AS20" s="33" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="AT20" s="33" t="s">
         <v>310</v>
@@ -7402,7 +7496,7 @@
         <v>97</v>
       </c>
       <c r="AY20" s="33" t="s">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="AZ20" s="33" t="s">
         <v>108</v>
@@ -7411,39 +7505,39 @@
         <v>8</v>
       </c>
       <c r="BB20" s="33" t="s">
-        <v>653</v>
-      </c>
-      <c r="BC20" s="36" t="s">
-        <v>657</v>
+        <v>647</v>
+      </c>
+      <c r="BC20" s="34" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:55" ht="62.1" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="D21" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>178</v>
+        <v>355</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>132</v>
+        <v>358</v>
       </c>
       <c r="J21" s="33" t="s">
         <v>91</v>
@@ -7455,7 +7549,7 @@
         <v>91</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>682</v>
+        <v>359</v>
       </c>
       <c r="N21" s="33" t="s">
         <v>97</v>
@@ -7467,10 +7561,10 @@
         <v>91</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="S21" s="33" t="s">
         <v>91</v>
@@ -7479,7 +7573,7 @@
         <v>91</v>
       </c>
       <c r="U21" s="33" t="s">
-        <v>168</v>
+        <v>362</v>
       </c>
       <c r="V21" s="33" t="s">
         <v>300</v>
@@ -7494,7 +7588,7 @@
         <v>301</v>
       </c>
       <c r="Z21" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AA21" s="33" t="s">
         <v>302</v>
@@ -7512,31 +7606,31 @@
         <v>91</v>
       </c>
       <c r="AF21" s="33" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="AG21" s="33" t="s">
-        <v>122</v>
+        <v>357</v>
       </c>
       <c r="AH21" s="33" t="s">
-        <v>686</v>
+        <v>364</v>
       </c>
       <c r="AI21" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>687</v>
+        <v>365</v>
       </c>
       <c r="AK21" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL21" s="33" t="s">
-        <v>376</v>
-      </c>
-      <c r="AM21" s="33">
-        <v>4</v>
-      </c>
-      <c r="AN21" s="33">
-        <v>3</v>
+        <v>366</v>
+      </c>
+      <c r="AM21" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN21" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AO21" s="33" t="s">
         <v>310</v>
@@ -7569,30 +7663,30 @@
         <v>97</v>
       </c>
       <c r="AY21" s="33" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AZ21" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA21" s="33" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
       <c r="BB21" s="33" t="s">
-        <v>638</v>
-      </c>
-      <c r="BC21" s="34" t="s">
-        <v>313</v>
+        <v>647</v>
+      </c>
+      <c r="BC21" s="36" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="1:55" ht="62.1" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D22" s="33" t="s">
         <v>295</v>
@@ -7601,16 +7695,16 @@
         <v>178</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="G22" s="33" t="s">
-        <v>122</v>
+        <v>372</v>
       </c>
       <c r="H22" s="33" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="I22" s="33" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J22" s="33" t="s">
         <v>91</v>
@@ -7622,7 +7716,7 @@
         <v>91</v>
       </c>
       <c r="M22" s="33" t="s">
-        <v>318</v>
+        <v>676</v>
       </c>
       <c r="N22" s="33" t="s">
         <v>97</v>
@@ -7634,10 +7728,10 @@
         <v>91</v>
       </c>
       <c r="Q22" s="33" t="s">
-        <v>382</v>
+        <v>679</v>
       </c>
       <c r="R22" s="33" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="S22" s="33" t="s">
         <v>91</v>
@@ -7646,13 +7740,13 @@
         <v>91</v>
       </c>
       <c r="U22" s="33" t="s">
-        <v>384</v>
+        <v>168</v>
       </c>
       <c r="V22" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W22" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X22" s="33" t="s">
         <v>300</v>
@@ -7672,38 +7766,38 @@
       <c r="AC22" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD22" s="33">
-        <v>60</v>
+      <c r="AD22" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="AE22" s="33" t="s">
-        <v>385</v>
+        <v>91</v>
       </c>
       <c r="AF22" s="33" t="s">
-        <v>121</v>
+        <v>321</v>
       </c>
       <c r="AG22" s="33" t="s">
         <v>122</v>
       </c>
       <c r="AH22" s="33" t="s">
-        <v>386</v>
+        <v>680</v>
       </c>
       <c r="AI22" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>387</v>
+        <v>681</v>
       </c>
       <c r="AK22" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL22" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="AM22" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN22" s="33" t="s">
-        <v>310</v>
+        <v>376</v>
+      </c>
+      <c r="AM22" s="33">
+        <v>4</v>
+      </c>
+      <c r="AN22" s="33">
+        <v>3</v>
       </c>
       <c r="AO22" s="33" t="s">
         <v>310</v>
@@ -7718,7 +7812,7 @@
         <v>310</v>
       </c>
       <c r="AS22" s="33" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="AT22" s="33" t="s">
         <v>310</v>
@@ -7745,7 +7839,7 @@
         <v>203</v>
       </c>
       <c r="BB22" s="33" t="s">
-        <v>109</v>
+        <v>633</v>
       </c>
       <c r="BC22" s="34" t="s">
         <v>313</v>
@@ -7753,13 +7847,13 @@
     </row>
     <row r="23" spans="1:55" ht="62.1" customHeight="1">
       <c r="A23" s="32" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>295</v>
@@ -7768,16 +7862,16 @@
         <v>178</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>393</v>
+        <v>122</v>
       </c>
       <c r="H23" s="33" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="J23" s="33" t="s">
         <v>91</v>
@@ -7789,7 +7883,7 @@
         <v>91</v>
       </c>
       <c r="M23" s="33" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="N23" s="33" t="s">
         <v>97</v>
@@ -7801,10 +7895,10 @@
         <v>91</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="R23" s="33" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="S23" s="33" t="s">
         <v>91</v>
@@ -7813,7 +7907,7 @@
         <v>91</v>
       </c>
       <c r="U23" s="33" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="V23" s="33" t="s">
         <v>300</v>
@@ -7831,40 +7925,40 @@
         <v>302</v>
       </c>
       <c r="AA23" s="33" t="s">
-        <v>302</v>
+        <v>648</v>
       </c>
       <c r="AB23" s="33" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
       <c r="AC23" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AD23" s="33">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AE23" s="33" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AF23" s="33" t="s">
         <v>121</v>
       </c>
       <c r="AG23" s="33" t="s">
-        <v>393</v>
+        <v>122</v>
       </c>
       <c r="AH23" s="33" t="s">
-        <v>398</v>
+        <v>682</v>
       </c>
       <c r="AI23" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="AK23" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL23" s="33" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="AM23" s="33" t="s">
         <v>310</v>
@@ -7885,7 +7979,7 @@
         <v>310</v>
       </c>
       <c r="AS23" s="33" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="AT23" s="33" t="s">
         <v>310</v>
@@ -7912,7 +8006,7 @@
         <v>203</v>
       </c>
       <c r="BB23" s="33" t="s">
-        <v>109</v>
+        <v>633</v>
       </c>
       <c r="BC23" s="34" t="s">
         <v>313</v>
@@ -7920,43 +8014,39 @@
     </row>
     <row r="24" spans="1:55" ht="62.1" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>401</v>
+        <v>191</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>402</v>
+        <v>698</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>403</v>
+        <v>699</v>
       </c>
       <c r="D24" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>404</v>
+        <v>700</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>405</v>
+        <v>698</v>
       </c>
       <c r="G24" s="33" t="s">
-        <v>406</v>
+        <v>701</v>
       </c>
       <c r="H24" s="33" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="I24" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="J24" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>91</v>
-      </c>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
       <c r="L24" s="33" t="s">
         <v>91</v>
       </c>
       <c r="M24" s="33" t="s">
-        <v>407</v>
+        <v>702</v>
       </c>
       <c r="N24" s="33" t="s">
         <v>97</v>
@@ -7964,151 +8054,147 @@
       <c r="O24" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="P24" s="33" t="s">
-        <v>91</v>
-      </c>
+      <c r="P24" s="33"/>
       <c r="Q24" s="33" t="s">
-        <v>408</v>
+        <v>703</v>
       </c>
       <c r="R24" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="S24" s="33" t="s">
-        <v>91</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="S24" s="33"/>
       <c r="T24" s="33" t="s">
-        <v>91</v>
+        <v>704</v>
       </c>
       <c r="U24" s="33" t="s">
-        <v>410</v>
+        <v>706</v>
       </c>
       <c r="V24" s="33" t="s">
-        <v>300</v>
+        <v>89</v>
       </c>
       <c r="W24" s="33" t="s">
-        <v>302</v>
+        <v>648</v>
       </c>
       <c r="X24" s="33" t="s">
-        <v>300</v>
+        <v>648</v>
       </c>
       <c r="Y24" s="33" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="Z24" s="33" t="s">
-        <v>300</v>
+        <v>666</v>
       </c>
       <c r="AA24" s="33" t="s">
-        <v>300</v>
+        <v>648</v>
       </c>
       <c r="AB24" s="33" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
       <c r="AC24" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD24" s="33" t="s">
-        <v>169</v>
+      <c r="AD24" s="33">
+        <v>180</v>
       </c>
       <c r="AE24" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AF24" s="33" t="s">
-        <v>411</v>
+        <v>707</v>
       </c>
       <c r="AG24" s="33" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="AH24" s="33" t="s">
-        <v>412</v>
+        <v>672</v>
       </c>
       <c r="AI24" s="33" t="s">
-        <v>306</v>
+        <v>708</v>
       </c>
       <c r="AJ24" s="33" t="s">
-        <v>413</v>
+        <v>709</v>
       </c>
       <c r="AK24" s="33" t="s">
-        <v>308</v>
+        <v>708</v>
       </c>
       <c r="AL24" s="33" t="s">
-        <v>414</v>
-      </c>
-      <c r="AM24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AO24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AP24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR24" s="33" t="s">
-        <v>310</v>
+        <v>710</v>
+      </c>
+      <c r="AM24" s="33">
+        <v>4</v>
+      </c>
+      <c r="AN24" s="33">
+        <v>3</v>
+      </c>
+      <c r="AO24" s="33">
+        <v>0.9</v>
+      </c>
+      <c r="AP24" s="33">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="33">
+        <v>9</v>
+      </c>
+      <c r="AR24" s="33">
+        <v>1.25</v>
       </c>
       <c r="AS24" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="AT24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AU24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AV24" s="33" t="s">
-        <v>310</v>
+        <v>711</v>
+      </c>
+      <c r="AT24" s="33">
+        <v>1</v>
+      </c>
+      <c r="AU24" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="AV24" s="33">
+        <v>0</v>
       </c>
       <c r="AW24" s="33" t="s">
         <v>311</v>
       </c>
       <c r="AX24" s="33" t="s">
-        <v>97</v>
+        <v>666</v>
       </c>
       <c r="AY24" s="33" t="s">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="AZ24" s="33" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="BA24" s="33" t="s">
         <v>203</v>
       </c>
       <c r="BB24" s="33" t="s">
-        <v>109</v>
+        <v>633</v>
       </c>
       <c r="BC24" s="34" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="25" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" ht="62.1" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>419</v>
+        <v>178</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>419</v>
+        <v>122</v>
       </c>
       <c r="H25" s="33" t="s">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="I25" s="33" t="s">
         <v>132</v>
@@ -8123,7 +8209,7 @@
         <v>91</v>
       </c>
       <c r="M25" s="33" t="s">
-        <v>272</v>
+        <v>683</v>
       </c>
       <c r="N25" s="33" t="s">
         <v>97</v>
@@ -8135,10 +8221,10 @@
         <v>91</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="R25" s="33" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="S25" s="33" t="s">
         <v>91</v>
@@ -8147,16 +8233,16 @@
         <v>91</v>
       </c>
       <c r="U25" s="33" t="s">
-        <v>423</v>
+        <v>394</v>
       </c>
       <c r="V25" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W25" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X25" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y25" s="33" t="s">
         <v>301</v>
@@ -8168,40 +8254,40 @@
         <v>302</v>
       </c>
       <c r="AB25" s="33" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
       <c r="AC25" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD25" s="33" t="s">
-        <v>169</v>
+      <c r="AD25" s="33">
+        <v>210</v>
       </c>
       <c r="AE25" s="33" t="s">
-        <v>91</v>
+        <v>395</v>
       </c>
       <c r="AF25" s="33" t="s">
-        <v>424</v>
+        <v>121</v>
       </c>
       <c r="AG25" s="33" t="s">
-        <v>419</v>
+        <v>122</v>
       </c>
       <c r="AH25" s="33" t="s">
-        <v>425</v>
+        <v>684</v>
       </c>
       <c r="AI25" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>426</v>
+        <v>685</v>
       </c>
       <c r="AK25" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL25" s="33" t="s">
-        <v>427</v>
-      </c>
-      <c r="AM25" s="33" t="s">
-        <v>310</v>
+        <v>396</v>
+      </c>
+      <c r="AM25" s="33">
+        <v>6</v>
       </c>
       <c r="AN25" s="33" t="s">
         <v>310</v>
@@ -8219,16 +8305,16 @@
         <v>310</v>
       </c>
       <c r="AS25" s="33" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="AT25" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="AU25" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AV25" s="33" t="s">
-        <v>310</v>
+      <c r="AU25" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="AV25" s="33">
+        <v>0.45</v>
       </c>
       <c r="AW25" s="33" t="s">
         <v>311</v>
@@ -8243,42 +8329,42 @@
         <v>108</v>
       </c>
       <c r="BA25" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB25" s="33" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="BC25" s="34" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="26" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" ht="62.1" customHeight="1">
       <c r="A26" s="32" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>148</v>
+        <v>402</v>
       </c>
       <c r="H26" s="33" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="I26" s="33" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="J26" s="33" t="s">
         <v>91</v>
@@ -8290,7 +8376,7 @@
         <v>91</v>
       </c>
       <c r="M26" s="33" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="N26" s="33" t="s">
         <v>97</v>
@@ -8302,10 +8388,10 @@
         <v>91</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="R26" s="33" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="S26" s="33" t="s">
         <v>91</v>
@@ -8314,64 +8400,64 @@
         <v>91</v>
       </c>
       <c r="U26" s="33" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="V26" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W26" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X26" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="Y26" s="35" t="s">
-        <v>97</v>
+      <c r="Y26" s="33" t="s">
+        <v>301</v>
       </c>
       <c r="Z26" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AA26" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB26" s="35" t="s">
-        <v>89</v>
+        <v>300</v>
+      </c>
+      <c r="AB26" s="33" t="s">
+        <v>303</v>
       </c>
       <c r="AC26" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD26" s="33">
-        <v>180</v>
+      <c r="AD26" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="AE26" s="33" t="s">
-        <v>436</v>
+        <v>91</v>
       </c>
       <c r="AF26" s="33" t="s">
-        <v>121</v>
+        <v>407</v>
       </c>
       <c r="AG26" s="33" t="s">
-        <v>437</v>
-      </c>
-      <c r="AH26" s="35" t="s">
-        <v>658</v>
+        <v>233</v>
+      </c>
+      <c r="AH26" s="33" t="s">
+        <v>408</v>
       </c>
       <c r="AI26" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="AK26" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL26" s="33" t="s">
-        <v>439</v>
-      </c>
-      <c r="AM26" s="33">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="33">
-        <v>2</v>
+        <v>410</v>
+      </c>
+      <c r="AM26" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN26" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AO26" s="33" t="s">
         <v>310</v>
@@ -8386,10 +8472,10 @@
         <v>310</v>
       </c>
       <c r="AS26" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT26" s="33">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="AT26" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AU26" s="33" t="s">
         <v>310</v>
@@ -8410,42 +8496,42 @@
         <v>108</v>
       </c>
       <c r="BA26" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB26" s="33" t="s">
-        <v>648</v>
-      </c>
-      <c r="BC26" s="36" t="s">
-        <v>660</v>
+        <v>642</v>
+      </c>
+      <c r="BC26" s="34" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="27" spans="1:55" ht="62.1" customHeight="1">
       <c r="A27" s="32" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>180</v>
+        <v>414</v>
       </c>
       <c r="H27" s="33" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="I27" s="33" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J27" s="33" t="s">
         <v>91</v>
@@ -8457,7 +8543,7 @@
         <v>91</v>
       </c>
       <c r="M27" s="33" t="s">
-        <v>445</v>
+        <v>272</v>
       </c>
       <c r="N27" s="33" t="s">
         <v>97</v>
@@ -8469,10 +8555,10 @@
         <v>91</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="R27" s="33" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="S27" s="33" t="s">
         <v>91</v>
@@ -8481,7 +8567,7 @@
         <v>91</v>
       </c>
       <c r="U27" s="33" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="V27" s="33" t="s">
         <v>300</v>
@@ -8490,16 +8576,16 @@
         <v>302</v>
       </c>
       <c r="X27" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y27" s="33" t="s">
         <v>301</v>
       </c>
       <c r="Z27" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA27" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AB27" s="33" t="s">
         <v>303</v>
@@ -8514,25 +8600,25 @@
         <v>91</v>
       </c>
       <c r="AF27" s="33" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="AG27" s="33" t="s">
-        <v>180</v>
+        <v>414</v>
       </c>
       <c r="AH27" s="33" t="s">
-        <v>141</v>
+        <v>420</v>
       </c>
       <c r="AI27" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ27" s="33" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="AK27" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL27" s="33" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="AM27" s="33" t="s">
         <v>310</v>
@@ -8553,7 +8639,7 @@
         <v>310</v>
       </c>
       <c r="AS27" s="33" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="AT27" s="33" t="s">
         <v>310</v>
@@ -8571,48 +8657,48 @@
         <v>97</v>
       </c>
       <c r="AY27" s="33" t="s">
-        <v>452</v>
+        <v>377</v>
       </c>
       <c r="AZ27" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA27" s="33" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
       <c r="BB27" s="33" t="s">
-        <v>109</v>
+        <v>647</v>
       </c>
       <c r="BC27" s="34" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="28" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="28" spans="1:55" ht="62.1" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="D28" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>457</v>
+        <v>81</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="G28" s="33" t="s">
-        <v>458</v>
+        <v>148</v>
       </c>
       <c r="H28" s="33" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="I28" s="33" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="J28" s="33" t="s">
         <v>91</v>
@@ -8623,8 +8709,8 @@
       <c r="L28" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="M28" s="35" t="s">
-        <v>661</v>
+      <c r="M28" s="33" t="s">
+        <v>428</v>
       </c>
       <c r="N28" s="33" t="s">
         <v>97</v>
@@ -8636,10 +8722,10 @@
         <v>91</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="R28" s="33" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="S28" s="33" t="s">
         <v>91</v>
@@ -8648,88 +8734,88 @@
         <v>91</v>
       </c>
       <c r="U28" s="33" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="V28" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W28" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y28" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z28" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="X28" s="33" t="s">
+      <c r="AA28" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Y28" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Z28" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="AA28" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB28" s="33" t="s">
-        <v>303</v>
+      <c r="AB28" s="35" t="s">
+        <v>89</v>
       </c>
       <c r="AC28" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD28" s="33" t="s">
-        <v>169</v>
+      <c r="AD28" s="33">
+        <v>180</v>
       </c>
       <c r="AE28" s="33" t="s">
-        <v>91</v>
+        <v>431</v>
       </c>
       <c r="AF28" s="33" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="AG28" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="AH28" s="33" t="s">
-        <v>463</v>
+        <v>432</v>
+      </c>
+      <c r="AH28" s="35" t="s">
+        <v>652</v>
       </c>
       <c r="AI28" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="AK28" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL28" s="33" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="AM28" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN28" s="33">
+        <v>2</v>
+      </c>
+      <c r="AO28" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AP28" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AQ28" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AR28" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AS28" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT28" s="33">
         <v>1</v>
       </c>
-      <c r="AO28" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AP28" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ28" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR28" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AS28" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="AT28" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AU28" s="33">
-        <v>0</v>
+      <c r="AU28" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AV28" s="33" t="s">
-        <v>466</v>
+        <v>310</v>
       </c>
       <c r="AW28" s="33" t="s">
         <v>311</v>
@@ -8738,7 +8824,7 @@
         <v>97</v>
       </c>
       <c r="AY28" s="33" t="s">
-        <v>452</v>
+        <v>377</v>
       </c>
       <c r="AZ28" s="33" t="s">
         <v>108</v>
@@ -8747,39 +8833,39 @@
         <v>8</v>
       </c>
       <c r="BB28" s="33" t="s">
-        <v>653</v>
-      </c>
-      <c r="BC28" s="34" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>642</v>
+      </c>
+      <c r="BC28" s="36" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55" ht="62.1" customHeight="1">
       <c r="A29" s="32" t="s">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>470</v>
+        <v>437</v>
       </c>
       <c r="D29" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>207</v>
+        <v>438</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="H29" s="33" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="J29" s="33" t="s">
         <v>91</v>
@@ -8790,8 +8876,8 @@
       <c r="L29" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="M29" s="35" t="s">
-        <v>662</v>
+      <c r="M29" s="33" t="s">
+        <v>688</v>
       </c>
       <c r="N29" s="33" t="s">
         <v>97</v>
@@ -8803,10 +8889,10 @@
         <v>91</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="R29" s="33" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="S29" s="33" t="s">
         <v>91</v>
@@ -8815,13 +8901,13 @@
         <v>91</v>
       </c>
       <c r="U29" s="33" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="V29" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W29" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X29" s="33" t="s">
         <v>300</v>
@@ -8830,46 +8916,46 @@
         <v>301</v>
       </c>
       <c r="Z29" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AA29" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB29" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB29" s="33" t="s">
         <v>303</v>
       </c>
       <c r="AC29" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="35" t="s">
-        <v>663</v>
+      <c r="AD29" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="AE29" s="33" t="s">
-        <v>475</v>
+        <v>91</v>
       </c>
       <c r="AF29" s="33" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="AG29" s="33" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="AH29" s="33" t="s">
-        <v>477</v>
+        <v>141</v>
       </c>
       <c r="AI29" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="AJ29" s="35" t="s">
-        <v>664</v>
-      </c>
-      <c r="AK29" s="35" t="s">
-        <v>665</v>
+      <c r="AJ29" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="AK29" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="AL29" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="AM29" s="33">
-        <v>6</v>
+        <v>446</v>
+      </c>
+      <c r="AM29" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AN29" s="33" t="s">
         <v>310</v>
@@ -8892,8 +8978,8 @@
       <c r="AT29" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="AU29" s="33">
-        <v>1</v>
+      <c r="AU29" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AV29" s="33" t="s">
         <v>310</v>
@@ -8905,48 +8991,48 @@
         <v>97</v>
       </c>
       <c r="AY29" s="33" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AZ29" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA29" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB29" s="33" t="s">
-        <v>648</v>
-      </c>
-      <c r="BC29" s="36" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>642</v>
+      </c>
+      <c r="BC29" s="34" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" ht="62.1" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="F30" s="33" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="G30" s="33" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H30" s="33" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="J30" s="33" t="s">
         <v>91</v>
@@ -8957,8 +9043,8 @@
       <c r="L30" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="M30" s="33" t="s">
-        <v>483</v>
+      <c r="M30" s="35" t="s">
+        <v>655</v>
       </c>
       <c r="N30" s="33" t="s">
         <v>97</v>
@@ -8970,10 +9056,10 @@
         <v>91</v>
       </c>
       <c r="Q30" s="33" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="R30" s="33" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="S30" s="33" t="s">
         <v>91</v>
@@ -8982,7 +9068,7 @@
         <v>91</v>
       </c>
       <c r="U30" s="33" t="s">
-        <v>486</v>
+        <v>457</v>
       </c>
       <c r="V30" s="33" t="s">
         <v>300</v>
@@ -8991,16 +9077,16 @@
         <v>302</v>
       </c>
       <c r="X30" s="33" t="s">
-        <v>654</v>
+        <v>302</v>
       </c>
       <c r="Y30" s="33" t="s">
         <v>301</v>
       </c>
       <c r="Z30" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AA30" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AB30" s="33" t="s">
         <v>303</v>
@@ -9015,31 +9101,31 @@
         <v>91</v>
       </c>
       <c r="AF30" s="33" t="s">
-        <v>424</v>
+        <v>233</v>
       </c>
       <c r="AG30" s="33" t="s">
-        <v>419</v>
+        <v>233</v>
       </c>
       <c r="AH30" s="33" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="AI30" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="AK30" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL30" s="33" t="s">
-        <v>489</v>
-      </c>
-      <c r="AM30" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN30" s="33" t="s">
-        <v>310</v>
+        <v>460</v>
+      </c>
+      <c r="AM30" s="33">
+        <v>6</v>
+      </c>
+      <c r="AN30" s="33">
+        <v>1</v>
       </c>
       <c r="AO30" s="33" t="s">
         <v>310</v>
@@ -9054,16 +9140,16 @@
         <v>310</v>
       </c>
       <c r="AS30" s="33" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="AT30" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="AU30" s="33" t="s">
-        <v>310</v>
+      <c r="AU30" s="33">
+        <v>0</v>
       </c>
       <c r="AV30" s="33" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AW30" s="33" t="s">
         <v>311</v>
@@ -9072,7 +9158,7 @@
         <v>97</v>
       </c>
       <c r="AY30" s="33" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AZ30" s="33" t="s">
         <v>108</v>
@@ -9081,36 +9167,36 @@
         <v>8</v>
       </c>
       <c r="BB30" s="33" t="s">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="BC30" s="34" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" ht="62.1" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>443</v>
+        <v>207</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="I31" s="33" t="s">
         <v>132</v>
@@ -9124,8 +9210,8 @@
       <c r="L31" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="M31" s="33" t="s">
-        <v>494</v>
+      <c r="M31" s="35" t="s">
+        <v>656</v>
       </c>
       <c r="N31" s="33" t="s">
         <v>97</v>
@@ -9137,10 +9223,10 @@
         <v>91</v>
       </c>
       <c r="Q31" s="33" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="R31" s="33" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="S31" s="33" t="s">
         <v>91</v>
@@ -9149,13 +9235,13 @@
         <v>91</v>
       </c>
       <c r="U31" s="33" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="V31" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W31" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X31" s="33" t="s">
         <v>300</v>
@@ -9164,46 +9250,46 @@
         <v>301</v>
       </c>
       <c r="Z31" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA31" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB31" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB31" s="35" t="s">
         <v>303</v>
       </c>
       <c r="AC31" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD31" s="33" t="s">
-        <v>169</v>
+      <c r="AD31" s="35" t="s">
+        <v>657</v>
       </c>
       <c r="AE31" s="33" t="s">
-        <v>91</v>
+        <v>470</v>
       </c>
       <c r="AF31" s="33" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="AG31" s="33" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="AH31" s="33" t="s">
-        <v>668</v>
+        <v>472</v>
       </c>
       <c r="AI31" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="AJ31" s="33" t="s">
-        <v>669</v>
-      </c>
-      <c r="AK31" s="33" t="s">
-        <v>308</v>
+      <c r="AJ31" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="AK31" s="35" t="s">
+        <v>659</v>
       </c>
       <c r="AL31" s="33" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="AM31" s="33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN31" s="33" t="s">
         <v>310</v>
@@ -9223,11 +9309,11 @@
       <c r="AS31" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="AT31" s="33">
-        <v>0.75</v>
-      </c>
-      <c r="AU31" s="33" t="s">
-        <v>310</v>
+      <c r="AT31" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU31" s="33">
+        <v>1</v>
       </c>
       <c r="AV31" s="33" t="s">
         <v>310</v>
@@ -9239,7 +9325,7 @@
         <v>97</v>
       </c>
       <c r="AY31" s="33" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="AZ31" s="33" t="s">
         <v>108</v>
@@ -9248,39 +9334,39 @@
         <v>8</v>
       </c>
       <c r="BB31" s="33" t="s">
-        <v>653</v>
-      </c>
-      <c r="BC31" s="34" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>642</v>
+      </c>
+      <c r="BC31" s="36" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55" ht="62.1" customHeight="1">
       <c r="A32" s="32" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="D32" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>122</v>
+        <v>414</v>
       </c>
       <c r="F32" s="33" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>122</v>
+        <v>414</v>
       </c>
       <c r="H32" s="33" t="s">
         <v>83</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="J32" s="33" t="s">
         <v>91</v>
@@ -9292,7 +9378,7 @@
         <v>91</v>
       </c>
       <c r="M32" s="33" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="N32" s="33" t="s">
         <v>97</v>
@@ -9304,10 +9390,10 @@
         <v>91</v>
       </c>
       <c r="Q32" s="33" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="R32" s="33" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="S32" s="33" t="s">
         <v>91</v>
@@ -9316,16 +9402,16 @@
         <v>91</v>
       </c>
       <c r="U32" s="33" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="V32" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W32" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X32" s="33" t="s">
-        <v>300</v>
+        <v>648</v>
       </c>
       <c r="Y32" s="33" t="s">
         <v>301</v>
@@ -9337,37 +9423,37 @@
         <v>302</v>
       </c>
       <c r="AB32" s="33" t="s">
-        <v>654</v>
+        <v>303</v>
       </c>
       <c r="AC32" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD32" s="33">
-        <v>180</v>
+      <c r="AD32" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="AE32" s="33" t="s">
-        <v>508</v>
+        <v>91</v>
       </c>
       <c r="AF32" s="33" t="s">
-        <v>509</v>
+        <v>419</v>
       </c>
       <c r="AG32" s="33" t="s">
-        <v>122</v>
+        <v>414</v>
       </c>
       <c r="AH32" s="33" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="AI32" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="AK32" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL32" s="33" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="AM32" s="33" t="s">
         <v>310</v>
@@ -9397,7 +9483,7 @@
         <v>310</v>
       </c>
       <c r="AV32" s="33" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AW32" s="33" t="s">
         <v>311</v>
@@ -9406,7 +9492,7 @@
         <v>97</v>
       </c>
       <c r="AY32" s="33" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="AZ32" s="33" t="s">
         <v>108</v>
@@ -9415,39 +9501,39 @@
         <v>8</v>
       </c>
       <c r="BB32" s="33" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="BC32" s="34" t="s">
-        <v>671</v>
+        <v>423</v>
       </c>
     </row>
     <row r="33" spans="1:55" ht="62.1" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="D33" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>458</v>
+        <v>180</v>
       </c>
       <c r="H33" s="33" t="s">
         <v>221</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J33" s="33" t="s">
         <v>91</v>
@@ -9459,7 +9545,7 @@
         <v>91</v>
       </c>
       <c r="M33" s="33" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="N33" s="33" t="s">
         <v>97</v>
@@ -9471,10 +9557,10 @@
         <v>91</v>
       </c>
       <c r="Q33" s="33" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="R33" s="33" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="S33" s="33" t="s">
         <v>91</v>
@@ -9483,7 +9569,7 @@
         <v>91</v>
       </c>
       <c r="U33" s="33" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="V33" s="33" t="s">
         <v>300</v>
@@ -9492,7 +9578,7 @@
         <v>302</v>
       </c>
       <c r="X33" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y33" s="33" t="s">
         <v>301</v>
@@ -9516,28 +9602,28 @@
         <v>91</v>
       </c>
       <c r="AF33" s="33" t="s">
-        <v>233</v>
+        <v>444</v>
       </c>
       <c r="AG33" s="33" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="AH33" s="33" t="s">
-        <v>521</v>
+        <v>662</v>
       </c>
       <c r="AI33" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>522</v>
+        <v>663</v>
       </c>
       <c r="AK33" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL33" s="33" t="s">
-        <v>523</v>
-      </c>
-      <c r="AM33" s="33" t="s">
-        <v>310</v>
+        <v>493</v>
+      </c>
+      <c r="AM33" s="33">
+        <v>4</v>
       </c>
       <c r="AN33" s="33" t="s">
         <v>310</v>
@@ -9557,8 +9643,8 @@
       <c r="AS33" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="AT33" s="33" t="s">
-        <v>310</v>
+      <c r="AT33" s="33">
+        <v>0.75</v>
       </c>
       <c r="AU33" s="33" t="s">
         <v>310</v>
@@ -9573,48 +9659,48 @@
         <v>97</v>
       </c>
       <c r="AY33" s="33" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AZ33" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA33" s="33" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
       <c r="BB33" s="33" t="s">
-        <v>109</v>
+        <v>647</v>
       </c>
       <c r="BC33" s="34" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="34" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" ht="62.1" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="D34" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="I34" s="33" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="J34" s="33" t="s">
         <v>91</v>
@@ -9626,7 +9712,7 @@
         <v>91</v>
       </c>
       <c r="M34" s="33" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="N34" s="33" t="s">
         <v>97</v>
@@ -9638,10 +9724,10 @@
         <v>91</v>
       </c>
       <c r="Q34" s="33" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="R34" s="33" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="S34" s="33" t="s">
         <v>91</v>
@@ -9650,61 +9736,61 @@
         <v>91</v>
       </c>
       <c r="U34" s="33" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="V34" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W34" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X34" s="33" t="s">
         <v>300</v>
       </c>
       <c r="Y34" s="33" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="Z34" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA34" s="33" t="s">
         <v>302</v>
       </c>
       <c r="AB34" s="33" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
       <c r="AC34" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AD34" s="33" t="s">
-        <v>169</v>
+      <c r="AD34" s="33">
+        <v>180</v>
       </c>
       <c r="AE34" s="33" t="s">
-        <v>91</v>
+        <v>503</v>
       </c>
       <c r="AF34" s="33" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="AG34" s="33" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="AH34" s="33" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="AI34" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="AK34" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL34" s="33" t="s">
-        <v>673</v>
-      </c>
-      <c r="AM34" s="33">
-        <v>10</v>
+        <v>507</v>
+      </c>
+      <c r="AM34" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AN34" s="33" t="s">
         <v>310</v>
@@ -9722,16 +9808,16 @@
         <v>310</v>
       </c>
       <c r="AS34" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="AT34" s="33">
-        <v>0.75</v>
+        <v>105</v>
+      </c>
+      <c r="AT34" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AU34" s="33" t="s">
         <v>310</v>
       </c>
       <c r="AV34" s="33" t="s">
-        <v>672</v>
+        <v>461</v>
       </c>
       <c r="AW34" s="33" t="s">
         <v>311</v>
@@ -9740,7 +9826,7 @@
         <v>97</v>
       </c>
       <c r="AY34" s="33" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AZ34" s="33" t="s">
         <v>108</v>
@@ -9749,39 +9835,39 @@
         <v>8</v>
       </c>
       <c r="BB34" s="33" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="BC34" s="34" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="35" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="35" spans="1:55" ht="62.1" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>538</v>
+        <v>510</v>
       </c>
       <c r="D35" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="I35" s="33" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="J35" s="33" t="s">
         <v>91</v>
@@ -9793,7 +9879,7 @@
         <v>91</v>
       </c>
       <c r="M35" s="33" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="N35" s="33" t="s">
         <v>97</v>
@@ -9805,10 +9891,10 @@
         <v>91</v>
       </c>
       <c r="Q35" s="33" t="s">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="R35" s="33" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="S35" s="33" t="s">
         <v>91</v>
@@ -9817,7 +9903,7 @@
         <v>91</v>
       </c>
       <c r="U35" s="33" t="s">
-        <v>423</v>
+        <v>515</v>
       </c>
       <c r="V35" s="33" t="s">
         <v>300</v>
@@ -9825,17 +9911,17 @@
       <c r="W35" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="X35" s="35" t="s">
-        <v>89</v>
+      <c r="X35" s="33" t="s">
+        <v>648</v>
       </c>
       <c r="Y35" s="33" t="s">
-        <v>97</v>
+        <v>301</v>
       </c>
       <c r="Z35" s="33" t="s">
-        <v>302</v>
+        <v>666</v>
       </c>
       <c r="AA35" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AB35" s="33" t="s">
         <v>303</v>
@@ -9850,31 +9936,31 @@
         <v>91</v>
       </c>
       <c r="AF35" s="33" t="s">
-        <v>424</v>
+        <v>233</v>
       </c>
       <c r="AG35" s="33" t="s">
-        <v>419</v>
+        <v>233</v>
       </c>
       <c r="AH35" s="33" t="s">
-        <v>675</v>
+        <v>516</v>
       </c>
       <c r="AI35" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="AK35" s="33" t="s">
-        <v>308</v>
+        <v>689</v>
       </c>
       <c r="AL35" s="33" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM35" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN35" s="33" t="s">
-        <v>310</v>
+        <v>518</v>
+      </c>
+      <c r="AM35" s="33">
+        <v>4</v>
+      </c>
+      <c r="AN35" s="33">
+        <v>1</v>
       </c>
       <c r="AO35" s="33" t="s">
         <v>310</v>
@@ -9889,16 +9975,16 @@
         <v>310</v>
       </c>
       <c r="AS35" s="33" t="s">
-        <v>676</v>
-      </c>
-      <c r="AT35" s="33">
-        <v>0.65</v>
+        <v>202</v>
+      </c>
+      <c r="AT35" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AU35" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="AV35" s="33" t="s">
-        <v>677</v>
+      <c r="AV35" s="33">
+        <v>0.9</v>
       </c>
       <c r="AW35" s="33" t="s">
         <v>311</v>
@@ -9907,30 +9993,30 @@
         <v>97</v>
       </c>
       <c r="AY35" s="33" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AZ35" s="33" t="s">
         <v>108</v>
       </c>
       <c r="BA35" s="33" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="BB35" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="BC35" s="34" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="36" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:55" ht="62.1" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>545</v>
+        <v>520</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>546</v>
+        <v>521</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>295</v>
@@ -9939,16 +10025,16 @@
         <v>207</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="G36" s="33" t="s">
-        <v>548</v>
+        <v>209</v>
       </c>
       <c r="H36" s="33" t="s">
         <v>221</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="J36" s="33" t="s">
         <v>91</v>
@@ -9960,7 +10046,7 @@
         <v>91</v>
       </c>
       <c r="M36" s="33" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="N36" s="33" t="s">
         <v>97</v>
@@ -9972,10 +10058,10 @@
         <v>91</v>
       </c>
       <c r="Q36" s="33" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="R36" s="33" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="S36" s="33" t="s">
         <v>91</v>
@@ -9984,19 +10070,19 @@
         <v>91</v>
       </c>
       <c r="U36" s="33" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="V36" s="33" t="s">
         <v>300</v>
       </c>
       <c r="W36" s="33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X36" s="33" t="s">
         <v>300</v>
       </c>
       <c r="Y36" s="33" t="s">
-        <v>301</v>
+        <v>666</v>
       </c>
       <c r="Z36" s="33" t="s">
         <v>300</v>
@@ -10014,31 +10100,31 @@
         <v>169</v>
       </c>
       <c r="AE36" s="33" t="s">
-        <v>553</v>
+        <v>91</v>
       </c>
       <c r="AF36" s="33" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="AG36" s="33" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="AH36" s="33" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="AI36" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="AK36" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL36" s="33" t="s">
-        <v>557</v>
-      </c>
-      <c r="AM36" s="33" t="s">
-        <v>310</v>
+        <v>667</v>
+      </c>
+      <c r="AM36" s="33">
+        <v>10</v>
       </c>
       <c r="AN36" s="33" t="s">
         <v>310</v>
@@ -10058,14 +10144,14 @@
       <c r="AS36" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="AT36" s="33" t="s">
-        <v>310</v>
+      <c r="AT36" s="33">
+        <v>0.75</v>
       </c>
       <c r="AU36" s="33" t="s">
         <v>310</v>
       </c>
       <c r="AV36" s="33" t="s">
-        <v>310</v>
+        <v>666</v>
       </c>
       <c r="AW36" s="33" t="s">
         <v>311</v>
@@ -10074,7 +10160,7 @@
         <v>97</v>
       </c>
       <c r="AY36" s="33" t="s">
-        <v>558</v>
+        <v>494</v>
       </c>
       <c r="AZ36" s="33" t="s">
         <v>108</v>
@@ -10083,36 +10169,36 @@
         <v>8</v>
       </c>
       <c r="BB36" s="33" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="BC36" s="34" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="37" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="37" spans="1:55" ht="62.1" customHeight="1">
       <c r="A37" s="32" t="s">
-        <v>559</v>
+        <v>531</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="D37" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="H37" s="33" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="I37" s="33" t="s">
         <v>132</v>
@@ -10127,7 +10213,7 @@
         <v>91</v>
       </c>
       <c r="M37" s="33" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="N37" s="33" t="s">
         <v>97</v>
@@ -10139,10 +10225,10 @@
         <v>91</v>
       </c>
       <c r="Q37" s="33" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="R37" s="33" t="s">
-        <v>565</v>
+        <v>536</v>
       </c>
       <c r="S37" s="33" t="s">
         <v>91</v>
@@ -10151,7 +10237,7 @@
         <v>91</v>
       </c>
       <c r="U37" s="33" t="s">
-        <v>566</v>
+        <v>418</v>
       </c>
       <c r="V37" s="33" t="s">
         <v>300</v>
@@ -10159,11 +10245,11 @@
       <c r="W37" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="X37" s="33" t="s">
-        <v>300</v>
+      <c r="X37" s="35" t="s">
+        <v>89</v>
       </c>
       <c r="Y37" s="33" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="Z37" s="33" t="s">
         <v>302</v>
@@ -10184,25 +10270,25 @@
         <v>91</v>
       </c>
       <c r="AF37" s="33" t="s">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="AG37" s="33" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="AH37" s="33" t="s">
-        <v>567</v>
+        <v>669</v>
       </c>
       <c r="AI37" s="33" t="s">
         <v>306</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="AK37" s="33" t="s">
         <v>308</v>
       </c>
       <c r="AL37" s="33" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
       <c r="AM37" s="33" t="s">
         <v>310</v>
@@ -10223,25 +10309,25 @@
         <v>310</v>
       </c>
       <c r="AS37" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="AT37" s="33" t="s">
-        <v>310</v>
+        <v>670</v>
+      </c>
+      <c r="AT37" s="33">
+        <v>0.65</v>
       </c>
       <c r="AU37" s="33" t="s">
         <v>310</v>
       </c>
       <c r="AV37" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW37" s="35" t="s">
+        <v>671</v>
+      </c>
+      <c r="AW37" s="33" t="s">
         <v>311</v>
       </c>
       <c r="AX37" s="33" t="s">
         <v>97</v>
       </c>
       <c r="AY37" s="33" t="s">
-        <v>570</v>
+        <v>494</v>
       </c>
       <c r="AZ37" s="33" t="s">
         <v>108</v>
@@ -10250,120 +10336,220 @@
         <v>8</v>
       </c>
       <c r="BB37" s="33" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="BC37" s="34" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="38" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A38" s="32"/>
-      <c r="B38" s="35" t="s">
-        <v>634</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>635</v>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="38" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A38" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>541</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="35" t="s">
-        <v>636</v>
+        <v>207</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>542</v>
       </c>
       <c r="G38" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="H38" s="35" t="s">
-        <v>83</v>
+        <v>543</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>221</v>
       </c>
       <c r="I38" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="33"/>
-      <c r="Y38" s="33"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="33"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
-      <c r="AD38" s="33"/>
-      <c r="AE38" s="33"/>
-      <c r="AF38" s="33"/>
-      <c r="AG38" s="33"/>
-      <c r="AH38" s="33"/>
-      <c r="AI38" s="33"/>
-      <c r="AJ38" s="33"/>
-      <c r="AK38" s="33"/>
-      <c r="AL38" s="33"/>
-      <c r="AM38" s="33"/>
-      <c r="AN38" s="33"/>
-      <c r="AO38" s="33"/>
-      <c r="AP38" s="33"/>
-      <c r="AQ38" s="33"/>
-      <c r="AR38" s="33"/>
-      <c r="AS38" s="33"/>
-      <c r="AT38" s="33"/>
-      <c r="AU38" s="33"/>
-      <c r="AV38" s="33"/>
-      <c r="AW38" s="33"/>
-      <c r="AX38" s="33"/>
-      <c r="AY38" s="33"/>
-      <c r="AZ38" s="33"/>
-      <c r="BA38" s="33"/>
-      <c r="BB38" s="33"/>
-      <c r="BC38" s="34"/>
-    </row>
-    <row r="39" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A39" s="32"/>
-      <c r="B39" s="35" t="s">
-        <v>641</v>
-      </c>
-      <c r="C39" s="35" t="s">
-        <v>642</v>
+        <v>358</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="K38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="L38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="M38" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="N38" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="O38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="P38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q38" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="R38" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="S38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="T38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="U38" s="33" t="s">
+        <v>547</v>
+      </c>
+      <c r="V38" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W38" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X38" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y38" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z38" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA38" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB38" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD38" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE38" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="AF38" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="AG38" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH38" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="AI38" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ38" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="AK38" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="AL38" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="AM38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AO38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AP38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AQ38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AR38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AS38" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV38" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW38" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX38" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY38" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="AZ38" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA38" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB38" s="33" t="s">
+        <v>647</v>
+      </c>
+      <c r="BC38" s="34" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A39" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>556</v>
       </c>
       <c r="D39" s="33" t="s">
         <v>295</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="F39" s="35" t="s">
-        <v>643</v>
+        <v>355</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>557</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>221</v>
+        <v>357</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>195</v>
       </c>
       <c r="I39" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="J39" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="35" t="s">
-        <v>644</v>
-      </c>
-      <c r="N39" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="K39" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="M39" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="N39" s="33" t="s">
         <v>97</v>
       </c>
       <c r="O39" s="33" t="s">
@@ -10373,40 +10559,40 @@
         <v>91</v>
       </c>
       <c r="Q39" s="33" t="s">
-        <v>183</v>
+        <v>559</v>
       </c>
       <c r="R39" s="33" t="s">
-        <v>184</v>
+        <v>560</v>
       </c>
       <c r="S39" s="33" t="s">
         <v>91</v>
       </c>
       <c r="T39" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="U39" s="35" t="s">
-        <v>645</v>
+        <v>91</v>
+      </c>
+      <c r="U39" s="33" t="s">
+        <v>561</v>
       </c>
       <c r="V39" s="33" t="s">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="W39" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="X39" s="35" t="s">
-        <v>89</v>
+        <v>302</v>
+      </c>
+      <c r="X39" s="33" t="s">
+        <v>300</v>
       </c>
       <c r="Y39" s="33" t="s">
-        <v>97</v>
+        <v>301</v>
       </c>
       <c r="Z39" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA39" s="35" t="s">
-        <v>97</v>
+        <v>302</v>
+      </c>
+      <c r="AA39" s="33" t="s">
+        <v>302</v>
       </c>
       <c r="AB39" s="33" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="AC39" s="33" t="s">
         <v>91</v>
@@ -10418,145 +10604,445 @@
         <v>91</v>
       </c>
       <c r="AF39" s="33" t="s">
-        <v>91</v>
+        <v>363</v>
       </c>
       <c r="AG39" s="33" t="s">
-        <v>180</v>
+        <v>357</v>
       </c>
       <c r="AH39" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI39" s="33"/>
-      <c r="AJ39" s="35" t="s">
-        <v>646</v>
+        <v>562</v>
+      </c>
+      <c r="AI39" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ39" s="33" t="s">
+        <v>563</v>
       </c>
       <c r="AK39" s="33" t="s">
-        <v>187</v>
+        <v>308</v>
       </c>
       <c r="AL39" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="AM39" s="33">
-        <v>1</v>
-      </c>
-      <c r="AN39" s="33">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="33">
-        <v>10</v>
-      </c>
-      <c r="AP39" s="33">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="33">
-        <v>12</v>
-      </c>
-      <c r="AR39" s="33">
-        <v>2.2000000000000002</v>
+        <v>564</v>
+      </c>
+      <c r="AM39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AO39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AP39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AQ39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AR39" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AS39" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="AT39" s="33">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="33">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="33">
-        <v>0</v>
+      <c r="AT39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU39" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV39" s="33" t="s">
+        <v>310</v>
       </c>
       <c r="AW39" s="35" t="s">
         <v>311</v>
       </c>
       <c r="AX39" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY39" s="33"/>
+        <v>97</v>
+      </c>
+      <c r="AY39" s="33" t="s">
+        <v>565</v>
+      </c>
       <c r="AZ39" s="33" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="BA39" s="33" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="BB39" s="33" t="s">
-        <v>638</v>
-      </c>
-      <c r="BC39" s="36" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="40" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+      <c r="BC39" s="34" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:55" ht="62.1" customHeight="1">
       <c r="A40" s="32"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="B40" s="35" t="s">
+        <v>629</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>630</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>631</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>84</v>
+      </c>
       <c r="J40" s="33"/>
       <c r="K40" s="33"/>
       <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
+      <c r="M40" s="33" t="s">
+        <v>696</v>
+      </c>
       <c r="N40" s="33"/>
       <c r="O40" s="33"/>
       <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
+      <c r="Q40" s="33" t="s">
+        <v>713</v>
+      </c>
+      <c r="R40" s="33" t="s">
+        <v>714</v>
+      </c>
       <c r="S40" s="33"/>
       <c r="T40" s="33"/>
-      <c r="U40" s="33"/>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="33"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
+      <c r="U40" s="33" t="s">
+        <v>715</v>
+      </c>
+      <c r="V40" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="W40" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="X40" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y40" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z40" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA40" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="AB40" s="35" t="s">
+        <v>89</v>
+      </c>
       <c r="AC40" s="33"/>
-      <c r="AD40" s="33"/>
-      <c r="AE40" s="33"/>
-      <c r="AF40" s="33"/>
-      <c r="AG40" s="33"/>
+      <c r="AD40" s="33">
+        <v>210</v>
+      </c>
+      <c r="AE40" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="AF40" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="AG40" s="33" t="s">
+        <v>717</v>
+      </c>
       <c r="AH40" s="33"/>
-      <c r="AI40" s="33"/>
-      <c r="AJ40" s="33"/>
-      <c r="AK40" s="33"/>
-      <c r="AL40" s="33"/>
-      <c r="AM40" s="33"/>
-      <c r="AN40" s="33"/>
-      <c r="AO40" s="33"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="33" t="s">
+        <v>718</v>
+      </c>
+      <c r="AK40" s="33" t="s">
+        <v>719</v>
+      </c>
+      <c r="AL40" s="33" t="s">
+        <v>720</v>
+      </c>
+      <c r="AM40" s="33">
+        <v>4</v>
+      </c>
+      <c r="AN40" s="33">
+        <v>4</v>
+      </c>
+      <c r="AO40" s="33">
+        <v>0.75</v>
+      </c>
       <c r="AP40" s="33"/>
-      <c r="AQ40" s="33"/>
-      <c r="AR40" s="33"/>
-      <c r="AS40" s="33"/>
-      <c r="AT40" s="33"/>
-      <c r="AU40" s="33"/>
-      <c r="AV40" s="33"/>
-      <c r="AW40" s="33"/>
-      <c r="AX40" s="33"/>
-      <c r="AY40" s="33"/>
-      <c r="AZ40" s="33"/>
-      <c r="BA40" s="33"/>
-      <c r="BB40" s="33"/>
-      <c r="BC40" s="34"/>
+      <c r="AQ40" s="33">
+        <v>4</v>
+      </c>
+      <c r="AR40" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="AS40" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT40" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="AU40" s="33">
+        <v>0.4</v>
+      </c>
+      <c r="AV40" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="AW40" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX40" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="AY40" s="33" t="s">
+        <v>721</v>
+      </c>
+      <c r="AZ40" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA40" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB40" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="BC40" s="34" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="41" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A41" s="32"/>
+      <c r="B41" s="35" t="s">
+        <v>636</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>637</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>638</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="35" t="s">
+        <v>639</v>
+      </c>
+      <c r="N41" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="O41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="P41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q41" s="33" t="s">
+        <v>693</v>
+      </c>
+      <c r="R41" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="U41" s="35" t="s">
+        <v>640</v>
+      </c>
+      <c r="V41" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="W41" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="X41" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y41" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z41" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA41" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB41" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD41" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG41" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="AH41" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI41" s="33"/>
+      <c r="AJ41" s="35" t="s">
+        <v>641</v>
+      </c>
+      <c r="AK41" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="AL41" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM41" s="33">
+        <v>2</v>
+      </c>
+      <c r="AN41" s="33">
+        <v>18</v>
+      </c>
+      <c r="AO41" s="33">
+        <v>10</v>
+      </c>
+      <c r="AP41" s="33">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="33">
+        <v>12</v>
+      </c>
+      <c r="AR41" s="33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AS41" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT41" s="33">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="33">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="33">
+        <v>0</v>
+      </c>
+      <c r="AW41" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX41" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AY41" s="33" t="s">
+        <v>694</v>
+      </c>
+      <c r="AZ41" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="BA41" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="BB41" s="33" t="s">
+        <v>633</v>
+      </c>
+      <c r="BC41" s="36" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="42" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A42" s="32"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="33"/>
+      <c r="V42" s="33"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="33"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="33"/>
+      <c r="AF42" s="33"/>
+      <c r="AG42" s="33"/>
+      <c r="AH42" s="33"/>
+      <c r="AI42" s="33"/>
+      <c r="AJ42" s="33"/>
+      <c r="AK42" s="33"/>
+      <c r="AL42" s="33"/>
+      <c r="AM42" s="33"/>
+      <c r="AN42" s="33"/>
+      <c r="AO42" s="33"/>
+      <c r="AP42" s="33"/>
+      <c r="AQ42" s="33"/>
+      <c r="AR42" s="33"/>
+      <c r="AS42" s="33"/>
+      <c r="AT42" s="33"/>
+      <c r="AU42" s="33"/>
+      <c r="AV42" s="33"/>
+      <c r="AW42" s="33"/>
+      <c r="AX42" s="33"/>
+      <c r="AY42" s="33"/>
+      <c r="AZ42" s="33"/>
+      <c r="BA42" s="33"/>
+      <c r="BB42" s="33"/>
+      <c r="BC42" s="34"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AY2:AY40">
+  <conditionalFormatting sqref="AY2:AY42">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Mixte"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB40">
+  <conditionalFormatting sqref="BB2:BB42">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Validé"/>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="À corriger"/>
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="À valider"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="BB2:BB40" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="BB2:BB42" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"À valider,Validé,À corriger,Refusé,À discuter"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="BA2:BA40" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="BA2:BA42" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10580,16 +11066,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27.95" customHeight="1">
@@ -10597,13 +11083,13 @@
         <v>78</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
@@ -10611,13 +11097,13 @@
         <v>78</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
@@ -10625,13 +11111,13 @@
         <v>78</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
@@ -10639,13 +11125,13 @@
         <v>78</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
@@ -10653,13 +11139,13 @@
         <v>78</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
@@ -10667,13 +11153,13 @@
         <v>111</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
@@ -10681,13 +11167,13 @@
         <v>111</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>116</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
@@ -10695,13 +11181,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
@@ -10709,13 +11195,13 @@
         <v>111</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
@@ -10723,13 +11209,13 @@
         <v>111</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
@@ -10737,13 +11223,13 @@
         <v>18</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
@@ -10751,13 +11237,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>134</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
@@ -10765,13 +11251,13 @@
         <v>18</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>135</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
@@ -10779,13 +11265,13 @@
         <v>18</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
@@ -10793,13 +11279,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
@@ -10807,13 +11293,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
@@ -10821,13 +11307,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>150</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
@@ -10835,13 +11321,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
@@ -10849,13 +11335,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
@@ -10863,13 +11349,13 @@
         <v>15</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
@@ -10877,13 +11363,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>165</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
@@ -10891,13 +11377,13 @@
         <v>9</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>165</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
@@ -10905,13 +11391,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
@@ -10919,13 +11405,13 @@
         <v>9</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
@@ -10933,13 +11419,13 @@
         <v>9</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
@@ -10947,13 +11433,13 @@
         <v>176</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
@@ -10961,13 +11447,13 @@
         <v>176</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>181</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
@@ -10975,13 +11461,13 @@
         <v>176</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
@@ -10989,13 +11475,13 @@
         <v>176</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
@@ -11003,13 +11489,13 @@
         <v>176</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>182</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
@@ -11017,13 +11503,13 @@
         <v>192</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
@@ -11031,13 +11517,13 @@
         <v>192</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>116</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
@@ -11045,13 +11531,13 @@
         <v>192</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
@@ -11059,13 +11545,13 @@
         <v>192</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="27.95" customHeight="1">
@@ -11073,13 +11559,13 @@
         <v>192</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="27.95" customHeight="1">
@@ -11087,13 +11573,13 @@
         <v>205</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27.95" customHeight="1">
@@ -11101,13 +11587,13 @@
         <v>205</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="27.95" customHeight="1">
@@ -11115,13 +11601,13 @@
         <v>205</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27.95" customHeight="1">
@@ -11129,13 +11615,13 @@
         <v>205</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>211</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="27.95" customHeight="1">
@@ -11143,13 +11629,13 @@
         <v>205</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>212</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.95" customHeight="1">
@@ -11157,13 +11643,13 @@
         <v>12</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="27.95" customHeight="1">
@@ -11171,13 +11657,13 @@
         <v>12</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>210</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="27.95" customHeight="1">
@@ -11185,13 +11671,13 @@
         <v>12</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="27.95" customHeight="1">
@@ -11199,13 +11685,13 @@
         <v>12</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>223</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="27.95" customHeight="1">
@@ -11213,13 +11699,13 @@
         <v>12</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="27.95" customHeight="1">
@@ -11227,13 +11713,13 @@
         <v>230</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>234</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="27.95" customHeight="1">
@@ -11241,13 +11727,13 @@
         <v>230</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>235</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="27.95" customHeight="1">
@@ -11255,13 +11741,13 @@
         <v>230</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="27.95" customHeight="1">
@@ -11269,13 +11755,13 @@
         <v>230</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="27.95" customHeight="1">
@@ -11283,13 +11769,13 @@
         <v>230</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>236</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="27.95" customHeight="1">
@@ -11297,13 +11783,13 @@
         <v>242</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="27.95" customHeight="1">
@@ -11311,13 +11797,13 @@
         <v>242</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>245</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="27.95" customHeight="1">
@@ -11325,13 +11811,13 @@
         <v>242</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>246</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="27.95" customHeight="1">
@@ -11339,13 +11825,13 @@
         <v>242</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>247</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="27.95" customHeight="1">
@@ -11353,13 +11839,13 @@
         <v>242</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="27.95" customHeight="1">
@@ -11367,13 +11853,13 @@
         <v>256</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>259</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.95" customHeight="1">
@@ -11381,13 +11867,13 @@
         <v>256</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>260</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27.95" customHeight="1">
@@ -11395,13 +11881,13 @@
         <v>256</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>261</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="27.95" customHeight="1">
@@ -11409,13 +11895,13 @@
         <v>256</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27.95" customHeight="1">
@@ -11423,13 +11909,13 @@
         <v>256</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>263</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="27.95" customHeight="1">
@@ -11437,13 +11923,13 @@
         <v>269</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>272</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="27.95" customHeight="1">
@@ -11451,13 +11937,13 @@
         <v>269</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>273</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="27.95" customHeight="1">
@@ -11465,13 +11951,13 @@
         <v>269</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>274</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27.95" customHeight="1">
@@ -11479,13 +11965,13 @@
         <v>269</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>118</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27.95" customHeight="1">
@@ -11493,13 +11979,13 @@
         <v>269</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="27.95" customHeight="1">
@@ -11507,13 +11993,13 @@
         <v>281</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="27.95" customHeight="1">
@@ -11521,13 +12007,13 @@
         <v>281</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>284</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="27.95" customHeight="1">
@@ -11535,13 +12021,13 @@
         <v>281</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>285</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="27.95" customHeight="1">
@@ -11549,13 +12035,13 @@
         <v>281</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>211</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="27.95" customHeight="1">
@@ -11563,13 +12049,13 @@
         <v>281</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>287</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="27.95" customHeight="1">
@@ -11577,7 +12063,7 @@
         <v>293</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>296</v>
@@ -11597,7 +12083,7 @@
         <v>297</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="27.95" customHeight="1">
@@ -11605,7 +12091,7 @@
         <v>315</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>318</v>
@@ -11625,7 +12111,7 @@
         <v>319</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="27.95" customHeight="1">
@@ -11633,7 +12119,7 @@
         <v>326</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>330</v>
@@ -11653,7 +12139,7 @@
         <v>331</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="27.95" customHeight="1">
@@ -11661,7 +12147,7 @@
         <v>338</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>342</v>
@@ -11681,7 +12167,7 @@
         <v>343</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="27.95" customHeight="1">
@@ -11689,7 +12175,7 @@
         <v>353</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>359</v>
@@ -11709,7 +12195,7 @@
         <v>360</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="27.95" customHeight="1">
@@ -11717,7 +12203,7 @@
         <v>370</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>373</v>
@@ -11737,7 +12223,7 @@
         <v>374</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="27.95" customHeight="1">
@@ -11745,7 +12231,7 @@
         <v>379</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>318</v>
@@ -11765,15 +12251,15 @@
         <v>382</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="27.95" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>272</v>
@@ -11784,27 +12270,27 @@
     </row>
     <row r="87" spans="1:4" ht="27.95" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="27.95" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D88" s="16" t="s">
         <v>377</v>
@@ -11812,24 +12298,24 @@
     </row>
     <row r="89" spans="1:4" ht="27.95" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="27.95" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>272</v>
@@ -11840,27 +12326,27 @@
     </row>
     <row r="91" spans="1:4" ht="27.95" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B91" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="27.95" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D92" s="16" t="s">
         <v>377</v>
@@ -11868,324 +12354,324 @@
     </row>
     <row r="93" spans="1:4" ht="27.95" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="27.95" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="27.95" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="27.95" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="27.95" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="27.95" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="27.95" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B99" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="27.95" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="27.95" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B101" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="27.95" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C102" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D102" s="16" t="s">
         <v>494</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="27.95" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B103" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="27.95" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="27.95" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="27.95" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="27.95" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="27.95" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="27.95" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B109" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="27.95" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="27.95" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="27.95" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="27.95" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="27.95" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="27.95" customHeight="1">
       <c r="A115" s="17" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>38</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -12209,7 +12695,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="40" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -12223,86 +12709,86 @@
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="20" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="44.1" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="44.1" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="44.1" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="44.1" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="44.1" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="44.1" customHeight="1">
@@ -12310,27 +12796,27 @@
         <v>75</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="44.1" customHeight="1">
       <c r="A11" s="23" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="44.1" customHeight="1">
@@ -12338,13 +12824,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="44.1" customHeight="1">
@@ -12352,13 +12838,13 @@
         <v>203</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="44.1" customHeight="1">
@@ -12366,27 +12852,27 @@
         <v>190</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="44.1" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>
